--- a/output/version3/test/10-5/MARL/IL/RL-RL/(RL+RL) test results.xlsx
+++ b/output/version3/test/10-5/MARL/IL/RL-RL/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>424</v>
+        <v>481</v>
       </c>
       <c r="C2" t="n">
-        <v>412</v>
+        <v>502</v>
       </c>
       <c r="D2" t="n">
-        <v>441</v>
+        <v>499</v>
       </c>
       <c r="E2" t="n">
-        <v>499</v>
+        <v>444</v>
       </c>
       <c r="F2" t="n">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="G2" t="n">
-        <v>468</v>
+        <v>411</v>
       </c>
       <c r="H2" t="n">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="I2" t="n">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="J2" t="n">
-        <v>501</v>
+        <v>427</v>
       </c>
       <c r="K2" t="n">
-        <v>502</v>
+        <v>466</v>
       </c>
       <c r="L2" t="n">
-        <v>457.6</v>
+        <v>456.5</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
+        <v>472</v>
+      </c>
+      <c r="C3" t="n">
+        <v>432</v>
+      </c>
+      <c r="D3" t="n">
+        <v>462</v>
+      </c>
+      <c r="E3" t="n">
+        <v>498</v>
+      </c>
+      <c r="F3" t="n">
         <v>477</v>
       </c>
-      <c r="C3" t="n">
-        <v>462</v>
-      </c>
-      <c r="D3" t="n">
-        <v>481</v>
-      </c>
-      <c r="E3" t="n">
-        <v>452</v>
-      </c>
-      <c r="F3" t="n">
-        <v>508</v>
-      </c>
       <c r="G3" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H3" t="n">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="I3" t="n">
-        <v>470</v>
+        <v>422</v>
       </c>
       <c r="J3" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K3" t="n">
-        <v>501</v>
+        <v>444</v>
       </c>
       <c r="L3" t="n">
-        <v>478.5</v>
+        <v>462.7</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="C4" t="n">
-        <v>474</v>
+        <v>549</v>
       </c>
       <c r="D4" t="n">
-        <v>516</v>
+        <v>445</v>
       </c>
       <c r="E4" t="n">
+        <v>528</v>
+      </c>
+      <c r="F4" t="n">
+        <v>469</v>
+      </c>
+      <c r="G4" t="n">
+        <v>534</v>
+      </c>
+      <c r="H4" t="n">
         <v>509</v>
       </c>
-      <c r="F4" t="n">
-        <v>537</v>
-      </c>
-      <c r="G4" t="n">
-        <v>553</v>
-      </c>
-      <c r="H4" t="n">
-        <v>522</v>
-      </c>
       <c r="I4" t="n">
-        <v>520</v>
+        <v>443</v>
       </c>
       <c r="J4" t="n">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="K4" t="n">
-        <v>471</v>
+        <v>541</v>
       </c>
       <c r="L4" t="n">
-        <v>507.1</v>
+        <v>496.2</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="C5" t="n">
-        <v>417</v>
+        <v>451</v>
       </c>
       <c r="D5" t="n">
+        <v>481</v>
+      </c>
+      <c r="E5" t="n">
+        <v>476</v>
+      </c>
+      <c r="F5" t="n">
         <v>449</v>
       </c>
-      <c r="E5" t="n">
-        <v>473</v>
-      </c>
-      <c r="F5" t="n">
-        <v>497</v>
-      </c>
       <c r="G5" t="n">
-        <v>482</v>
+        <v>449</v>
       </c>
       <c r="H5" t="n">
-        <v>449</v>
+        <v>477</v>
       </c>
       <c r="I5" t="n">
-        <v>508</v>
+        <v>478</v>
       </c>
       <c r="J5" t="n">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="K5" t="n">
-        <v>433</v>
+        <v>491</v>
       </c>
       <c r="L5" t="n">
-        <v>463.1</v>
+        <v>466.7</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>478</v>
+        <v>441</v>
       </c>
       <c r="C6" t="n">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="D6" t="n">
+        <v>516</v>
+      </c>
+      <c r="E6" t="n">
         <v>437</v>
       </c>
-      <c r="E6" t="n">
-        <v>423</v>
-      </c>
       <c r="F6" t="n">
+        <v>435</v>
+      </c>
+      <c r="G6" t="n">
+        <v>436</v>
+      </c>
+      <c r="H6" t="n">
+        <v>491</v>
+      </c>
+      <c r="I6" t="n">
+        <v>547</v>
+      </c>
+      <c r="J6" t="n">
+        <v>439</v>
+      </c>
+      <c r="K6" t="n">
         <v>490</v>
       </c>
-      <c r="G6" t="n">
-        <v>444</v>
-      </c>
-      <c r="H6" t="n">
-        <v>562</v>
-      </c>
-      <c r="I6" t="n">
-        <v>422</v>
-      </c>
-      <c r="J6" t="n">
-        <v>417</v>
-      </c>
-      <c r="K6" t="n">
-        <v>554</v>
-      </c>
       <c r="L6" t="n">
-        <v>472.5</v>
+        <v>473.9</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>421</v>
+        <v>452</v>
       </c>
       <c r="C7" t="n">
+        <v>398</v>
+      </c>
+      <c r="D7" t="n">
+        <v>457</v>
+      </c>
+      <c r="E7" t="n">
+        <v>429</v>
+      </c>
+      <c r="F7" t="n">
+        <v>419</v>
+      </c>
+      <c r="G7" t="n">
+        <v>434</v>
+      </c>
+      <c r="H7" t="n">
+        <v>481</v>
+      </c>
+      <c r="I7" t="n">
+        <v>445</v>
+      </c>
+      <c r="J7" t="n">
+        <v>479</v>
+      </c>
+      <c r="K7" t="n">
+        <v>476</v>
+      </c>
+      <c r="L7" t="n">
         <v>447</v>
-      </c>
-      <c r="D7" t="n">
-        <v>461</v>
-      </c>
-      <c r="E7" t="n">
-        <v>394</v>
-      </c>
-      <c r="F7" t="n">
-        <v>467</v>
-      </c>
-      <c r="G7" t="n">
-        <v>467</v>
-      </c>
-      <c r="H7" t="n">
-        <v>457</v>
-      </c>
-      <c r="I7" t="n">
-        <v>488</v>
-      </c>
-      <c r="J7" t="n">
-        <v>513</v>
-      </c>
-      <c r="K7" t="n">
-        <v>451</v>
-      </c>
-      <c r="L7" t="n">
-        <v>456.6</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>526</v>
+        <v>555</v>
       </c>
       <c r="C8" t="n">
-        <v>492</v>
+        <v>448</v>
       </c>
       <c r="D8" t="n">
-        <v>479</v>
+        <v>566</v>
       </c>
       <c r="E8" t="n">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="F8" t="n">
-        <v>451</v>
+        <v>506</v>
       </c>
       <c r="G8" t="n">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="H8" t="n">
-        <v>478</v>
+        <v>553</v>
       </c>
       <c r="I8" t="n">
-        <v>568</v>
+        <v>514</v>
       </c>
       <c r="J8" t="n">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="K8" t="n">
-        <v>472</v>
+        <v>518</v>
       </c>
       <c r="L8" t="n">
-        <v>496.1</v>
+        <v>516.5</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>444</v>
+        <v>481</v>
       </c>
       <c r="C9" t="n">
-        <v>507</v>
+        <v>458</v>
       </c>
       <c r="D9" t="n">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="E9" t="n">
-        <v>515</v>
+        <v>470</v>
       </c>
       <c r="F9" t="n">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="G9" t="n">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="H9" t="n">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="I9" t="n">
-        <v>419</v>
+        <v>517</v>
       </c>
       <c r="J9" t="n">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="K9" t="n">
-        <v>424</v>
+        <v>455</v>
       </c>
       <c r="L9" t="n">
-        <v>452.3</v>
+        <v>461.2</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>487</v>
+        <v>442</v>
       </c>
       <c r="C10" t="n">
-        <v>430</v>
+        <v>507</v>
       </c>
       <c r="D10" t="n">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="E10" t="n">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="F10" t="n">
-        <v>550</v>
+        <v>514</v>
       </c>
       <c r="G10" t="n">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H10" t="n">
+        <v>450</v>
+      </c>
+      <c r="I10" t="n">
+        <v>534</v>
+      </c>
+      <c r="J10" t="n">
         <v>507</v>
       </c>
-      <c r="I10" t="n">
-        <v>519</v>
-      </c>
-      <c r="J10" t="n">
-        <v>502</v>
-      </c>
       <c r="K10" t="n">
-        <v>499</v>
+        <v>454</v>
       </c>
       <c r="L10" t="n">
-        <v>491.6</v>
+        <v>486.4</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="C11" t="n">
-        <v>469</v>
+        <v>447</v>
       </c>
       <c r="D11" t="n">
-        <v>435</v>
+        <v>399</v>
       </c>
       <c r="E11" t="n">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="F11" t="n">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="G11" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="H11" t="n">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="I11" t="n">
-        <v>457</v>
+        <v>423</v>
       </c>
       <c r="J11" t="n">
-        <v>392</v>
+        <v>452</v>
       </c>
       <c r="K11" t="n">
-        <v>456</v>
+        <v>409</v>
       </c>
       <c r="L11" t="n">
-        <v>432.8</v>
+        <v>425.9</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>537</v>
+        <v>487</v>
       </c>
       <c r="C12" t="n">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="D12" t="n">
-        <v>539</v>
+        <v>505</v>
       </c>
       <c r="E12" t="n">
-        <v>435</v>
+        <v>503</v>
       </c>
       <c r="F12" t="n">
-        <v>504</v>
+        <v>562</v>
       </c>
       <c r="G12" t="n">
-        <v>601</v>
+        <v>517</v>
       </c>
       <c r="H12" t="n">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="I12" t="n">
-        <v>468</v>
+        <v>514</v>
       </c>
       <c r="J12" t="n">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="K12" t="n">
-        <v>556</v>
+        <v>517</v>
       </c>
       <c r="L12" t="n">
-        <v>513.2</v>
+        <v>505.7</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>421</v>
+        <v>494</v>
       </c>
       <c r="C13" t="n">
-        <v>466</v>
+        <v>521</v>
       </c>
       <c r="D13" t="n">
-        <v>555</v>
+        <v>437</v>
       </c>
       <c r="E13" t="n">
-        <v>537</v>
+        <v>493</v>
       </c>
       <c r="F13" t="n">
-        <v>534</v>
+        <v>495</v>
       </c>
       <c r="G13" t="n">
-        <v>494</v>
+        <v>447</v>
       </c>
       <c r="H13" t="n">
-        <v>445</v>
+        <v>496</v>
       </c>
       <c r="I13" t="n">
-        <v>460</v>
+        <v>433</v>
       </c>
       <c r="J13" t="n">
-        <v>492</v>
+        <v>408</v>
       </c>
       <c r="K13" t="n">
-        <v>488</v>
+        <v>418</v>
       </c>
       <c r="L13" t="n">
-        <v>489.2</v>
+        <v>464.2</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>489</v>
+        <v>550</v>
       </c>
       <c r="C14" t="n">
-        <v>483</v>
+        <v>549</v>
       </c>
       <c r="D14" t="n">
+        <v>528</v>
+      </c>
+      <c r="E14" t="n">
+        <v>494</v>
+      </c>
+      <c r="F14" t="n">
+        <v>477</v>
+      </c>
+      <c r="G14" t="n">
+        <v>514</v>
+      </c>
+      <c r="H14" t="n">
+        <v>545</v>
+      </c>
+      <c r="I14" t="n">
         <v>556</v>
       </c>
-      <c r="E14" t="n">
-        <v>509</v>
-      </c>
-      <c r="F14" t="n">
-        <v>535</v>
-      </c>
-      <c r="G14" t="n">
-        <v>534</v>
-      </c>
-      <c r="H14" t="n">
-        <v>501</v>
-      </c>
-      <c r="I14" t="n">
-        <v>497</v>
-      </c>
       <c r="J14" t="n">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="K14" t="n">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="L14" t="n">
-        <v>509.4</v>
+        <v>517.7</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="C15" t="n">
-        <v>478</v>
+        <v>503</v>
       </c>
       <c r="D15" t="n">
+        <v>482</v>
+      </c>
+      <c r="E15" t="n">
+        <v>462</v>
+      </c>
+      <c r="F15" t="n">
         <v>474</v>
       </c>
-      <c r="E15" t="n">
-        <v>430</v>
-      </c>
-      <c r="F15" t="n">
-        <v>435</v>
-      </c>
       <c r="G15" t="n">
-        <v>451</v>
+        <v>498</v>
       </c>
       <c r="H15" t="n">
-        <v>468</v>
+        <v>419</v>
       </c>
       <c r="I15" t="n">
-        <v>476</v>
+        <v>499</v>
       </c>
       <c r="J15" t="n">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="K15" t="n">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="L15" t="n">
-        <v>465.2</v>
+        <v>470.6</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="C16" t="n">
-        <v>445</v>
+        <v>489</v>
       </c>
       <c r="D16" t="n">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="E16" t="n">
-        <v>498</v>
+        <v>479</v>
       </c>
       <c r="F16" t="n">
-        <v>474</v>
+        <v>443</v>
       </c>
       <c r="G16" t="n">
-        <v>554</v>
+        <v>519</v>
       </c>
       <c r="H16" t="n">
-        <v>484</v>
+        <v>534</v>
       </c>
       <c r="I16" t="n">
-        <v>508</v>
+        <v>476</v>
       </c>
       <c r="J16" t="n">
-        <v>449</v>
+        <v>509</v>
       </c>
       <c r="K16" t="n">
-        <v>496</v>
+        <v>466</v>
       </c>
       <c r="L16" t="n">
-        <v>488.6</v>
+        <v>486.5</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>488</v>
+        <v>451</v>
       </c>
       <c r="C17" t="n">
-        <v>505</v>
+        <v>423</v>
       </c>
       <c r="D17" t="n">
-        <v>523</v>
+        <v>482</v>
       </c>
       <c r="E17" t="n">
-        <v>495</v>
+        <v>447</v>
       </c>
       <c r="F17" t="n">
-        <v>434</v>
+        <v>524</v>
       </c>
       <c r="G17" t="n">
-        <v>488</v>
+        <v>468</v>
       </c>
       <c r="H17" t="n">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="I17" t="n">
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="J17" t="n">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="K17" t="n">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="L17" t="n">
-        <v>479.3</v>
+        <v>466.3</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="C18" t="n">
-        <v>449</v>
+        <v>522</v>
       </c>
       <c r="D18" t="n">
-        <v>541</v>
+        <v>485</v>
       </c>
       <c r="E18" t="n">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F18" t="n">
-        <v>575</v>
+        <v>460</v>
       </c>
       <c r="G18" t="n">
-        <v>533</v>
+        <v>471</v>
       </c>
       <c r="H18" t="n">
-        <v>560</v>
+        <v>489</v>
       </c>
       <c r="I18" t="n">
-        <v>528</v>
+        <v>546</v>
       </c>
       <c r="J18" t="n">
-        <v>553</v>
+        <v>525</v>
       </c>
       <c r="K18" t="n">
-        <v>467</v>
+        <v>525</v>
       </c>
       <c r="L18" t="n">
-        <v>515.9</v>
+        <v>499.1</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C19" t="n">
-        <v>486</v>
+        <v>548</v>
       </c>
       <c r="D19" t="n">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="E19" t="n">
-        <v>478</v>
+        <v>522</v>
       </c>
       <c r="F19" t="n">
-        <v>526</v>
+        <v>444</v>
       </c>
       <c r="G19" t="n">
-        <v>486</v>
+        <v>524</v>
       </c>
       <c r="H19" t="n">
-        <v>504</v>
+        <v>469</v>
       </c>
       <c r="I19" t="n">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="J19" t="n">
-        <v>553</v>
+        <v>501</v>
       </c>
       <c r="K19" t="n">
-        <v>486</v>
+        <v>524</v>
       </c>
       <c r="L19" t="n">
-        <v>497.9</v>
+        <v>502.8</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>508</v>
+        <v>562</v>
       </c>
       <c r="C20" t="n">
-        <v>500</v>
+        <v>429</v>
       </c>
       <c r="D20" t="n">
-        <v>467</v>
+        <v>580</v>
       </c>
       <c r="E20" t="n">
-        <v>525</v>
+        <v>487</v>
       </c>
       <c r="F20" t="n">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="G20" t="n">
-        <v>463</v>
+        <v>435</v>
       </c>
       <c r="H20" t="n">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="I20" t="n">
-        <v>505</v>
+        <v>451</v>
       </c>
       <c r="J20" t="n">
-        <v>605</v>
+        <v>544</v>
       </c>
       <c r="K20" t="n">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="L20" t="n">
-        <v>501.8</v>
+        <v>495.7</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>518</v>
+        <v>422</v>
       </c>
       <c r="C21" t="n">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="D21" t="n">
-        <v>516</v>
+        <v>428</v>
       </c>
       <c r="E21" t="n">
         <v>417</v>
       </c>
       <c r="F21" t="n">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="G21" t="n">
-        <v>457</v>
+        <v>513</v>
       </c>
       <c r="H21" t="n">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I21" t="n">
-        <v>440</v>
+        <v>506</v>
       </c>
       <c r="J21" t="n">
-        <v>433</v>
+        <v>478</v>
       </c>
       <c r="K21" t="n">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="L21" t="n">
-        <v>456.5</v>
+        <v>449.6</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>473</v>
+        <v>452</v>
       </c>
       <c r="C22" t="n">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="D22" t="n">
-        <v>445</v>
+        <v>515</v>
       </c>
       <c r="E22" t="n">
-        <v>419</v>
+        <v>513</v>
       </c>
       <c r="F22" t="n">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="G22" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="H22" t="n">
-        <v>457</v>
+        <v>425</v>
       </c>
       <c r="I22" t="n">
-        <v>440</v>
+        <v>485</v>
       </c>
       <c r="J22" t="n">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="K22" t="n">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="L22" t="n">
-        <v>438.9</v>
+        <v>467.8</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="C23" t="n">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="D23" t="n">
+        <v>420</v>
+      </c>
+      <c r="E23" t="n">
+        <v>455</v>
+      </c>
+      <c r="F23" t="n">
         <v>452</v>
       </c>
-      <c r="E23" t="n">
-        <v>414</v>
-      </c>
-      <c r="F23" t="n">
-        <v>425</v>
-      </c>
       <c r="G23" t="n">
-        <v>409</v>
+        <v>377</v>
       </c>
       <c r="H23" t="n">
+        <v>424</v>
+      </c>
+      <c r="I23" t="n">
+        <v>484</v>
+      </c>
+      <c r="J23" t="n">
         <v>441</v>
       </c>
-      <c r="I23" t="n">
-        <v>469</v>
-      </c>
-      <c r="J23" t="n">
-        <v>420</v>
-      </c>
       <c r="K23" t="n">
-        <v>422</v>
+        <v>477</v>
       </c>
       <c r="L23" t="n">
-        <v>427.6</v>
+        <v>436.3</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="C24" t="n">
-        <v>413</v>
+        <v>462</v>
       </c>
       <c r="D24" t="n">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="E24" t="n">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F24" t="n">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="G24" t="n">
-        <v>447</v>
+        <v>400</v>
       </c>
       <c r="H24" t="n">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="I24" t="n">
-        <v>500</v>
+        <v>394</v>
       </c>
       <c r="J24" t="n">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="K24" t="n">
-        <v>520</v>
+        <v>465</v>
       </c>
       <c r="L24" t="n">
-        <v>446</v>
+        <v>426.2</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>448</v>
+        <v>412</v>
       </c>
       <c r="C25" t="n">
+        <v>401</v>
+      </c>
+      <c r="D25" t="n">
+        <v>371</v>
+      </c>
+      <c r="E25" t="n">
         <v>421</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
+        <v>420</v>
+      </c>
+      <c r="G25" t="n">
+        <v>431</v>
+      </c>
+      <c r="H25" t="n">
+        <v>417</v>
+      </c>
+      <c r="I25" t="n">
+        <v>385</v>
+      </c>
+      <c r="J25" t="n">
         <v>439</v>
       </c>
-      <c r="E25" t="n">
-        <v>473</v>
-      </c>
-      <c r="F25" t="n">
-        <v>414</v>
-      </c>
-      <c r="G25" t="n">
-        <v>402</v>
-      </c>
-      <c r="H25" t="n">
-        <v>412</v>
-      </c>
-      <c r="I25" t="n">
-        <v>415</v>
-      </c>
-      <c r="J25" t="n">
-        <v>385</v>
-      </c>
       <c r="K25" t="n">
-        <v>382</v>
+        <v>479</v>
       </c>
       <c r="L25" t="n">
-        <v>419.1</v>
+        <v>417.6</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="C26" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D26" t="n">
-        <v>561</v>
+        <v>588</v>
       </c>
       <c r="E26" t="n">
-        <v>570</v>
+        <v>516</v>
       </c>
       <c r="F26" t="n">
-        <v>518</v>
+        <v>554</v>
       </c>
       <c r="G26" t="n">
-        <v>465</v>
+        <v>538</v>
       </c>
       <c r="H26" t="n">
-        <v>485</v>
+        <v>606</v>
       </c>
       <c r="I26" t="n">
-        <v>545</v>
+        <v>499</v>
       </c>
       <c r="J26" t="n">
-        <v>540</v>
+        <v>507</v>
       </c>
       <c r="K26" t="n">
-        <v>636</v>
+        <v>594</v>
       </c>
       <c r="L26" t="n">
-        <v>542.6</v>
+        <v>550</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
+        <v>438</v>
+      </c>
+      <c r="C27" t="n">
+        <v>455</v>
+      </c>
+      <c r="D27" t="n">
+        <v>402</v>
+      </c>
+      <c r="E27" t="n">
+        <v>424</v>
+      </c>
+      <c r="F27" t="n">
+        <v>476</v>
+      </c>
+      <c r="G27" t="n">
         <v>457</v>
       </c>
-      <c r="C27" t="n">
-        <v>413</v>
-      </c>
-      <c r="D27" t="n">
-        <v>447</v>
-      </c>
-      <c r="E27" t="n">
-        <v>468</v>
-      </c>
-      <c r="F27" t="n">
-        <v>524</v>
-      </c>
-      <c r="G27" t="n">
-        <v>429</v>
-      </c>
       <c r="H27" t="n">
-        <v>467</v>
+        <v>408</v>
       </c>
       <c r="I27" t="n">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="J27" t="n">
-        <v>441</v>
+        <v>463</v>
       </c>
       <c r="K27" t="n">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="L27" t="n">
-        <v>456.7</v>
+        <v>443.7</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>509</v>
+        <v>447</v>
       </c>
       <c r="C28" t="n">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="D28" t="n">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E28" t="n">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="F28" t="n">
-        <v>477</v>
+        <v>441</v>
       </c>
       <c r="G28" t="n">
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="H28" t="n">
+        <v>437</v>
+      </c>
+      <c r="I28" t="n">
+        <v>452</v>
+      </c>
+      <c r="J28" t="n">
         <v>450</v>
       </c>
-      <c r="I28" t="n">
-        <v>451</v>
-      </c>
-      <c r="J28" t="n">
-        <v>444</v>
-      </c>
       <c r="K28" t="n">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="L28" t="n">
-        <v>457</v>
+        <v>449.1</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>462</v>
+        <v>426</v>
       </c>
       <c r="C29" t="n">
+        <v>471</v>
+      </c>
+      <c r="D29" t="n">
         <v>392</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
+        <v>433</v>
+      </c>
+      <c r="F29" t="n">
         <v>450</v>
       </c>
-      <c r="E29" t="n">
-        <v>419</v>
-      </c>
-      <c r="F29" t="n">
-        <v>441</v>
-      </c>
       <c r="G29" t="n">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="H29" t="n">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="I29" t="n">
-        <v>470</v>
+        <v>403</v>
       </c>
       <c r="J29" t="n">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="K29" t="n">
-        <v>363</v>
+        <v>417</v>
       </c>
       <c r="L29" t="n">
-        <v>426.5</v>
+        <v>431.1</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="C30" t="n">
-        <v>449</v>
+        <v>475</v>
       </c>
       <c r="D30" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E30" t="n">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="F30" t="n">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="G30" t="n">
-        <v>447</v>
+        <v>361</v>
       </c>
       <c r="H30" t="n">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="I30" t="n">
-        <v>524</v>
+        <v>455</v>
       </c>
       <c r="J30" t="n">
-        <v>417</v>
+        <v>493</v>
       </c>
       <c r="K30" t="n">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="L30" t="n">
-        <v>457.9</v>
+        <v>438.8</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>436</v>
+        <v>406</v>
       </c>
       <c r="C31" t="n">
-        <v>473</v>
+        <v>508</v>
       </c>
       <c r="D31" t="n">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="E31" t="n">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="F31" t="n">
-        <v>516</v>
+        <v>481</v>
       </c>
       <c r="G31" t="n">
-        <v>422</v>
+        <v>485</v>
       </c>
       <c r="H31" t="n">
-        <v>520</v>
+        <v>365</v>
       </c>
       <c r="I31" t="n">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="J31" t="n">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="K31" t="n">
-        <v>452</v>
+        <v>407</v>
       </c>
       <c r="L31" t="n">
-        <v>447.5</v>
+        <v>433</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="C32" t="n">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="D32" t="n">
-        <v>427</v>
+        <v>462</v>
       </c>
       <c r="E32" t="n">
-        <v>431</v>
+        <v>409</v>
       </c>
       <c r="F32" t="n">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="G32" t="n">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="H32" t="n">
-        <v>379</v>
+        <v>502</v>
       </c>
       <c r="I32" t="n">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="J32" t="n">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="K32" t="n">
-        <v>486</v>
+        <v>413</v>
       </c>
       <c r="L32" t="n">
-        <v>437.1</v>
+        <v>447.6</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>425</v>
+        <v>388</v>
       </c>
       <c r="C33" t="n">
-        <v>401</v>
+        <v>447</v>
       </c>
       <c r="D33" t="n">
-        <v>443</v>
+        <v>410</v>
       </c>
       <c r="E33" t="n">
-        <v>420</v>
+        <v>371</v>
       </c>
       <c r="F33" t="n">
-        <v>443</v>
+        <v>391</v>
       </c>
       <c r="G33" t="n">
-        <v>438</v>
+        <v>400</v>
       </c>
       <c r="H33" t="n">
-        <v>447</v>
+        <v>408</v>
       </c>
       <c r="I33" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J33" t="n">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="K33" t="n">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="L33" t="n">
-        <v>421.2</v>
+        <v>402.5</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="C34" t="n">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="D34" t="n">
+        <v>442</v>
+      </c>
+      <c r="E34" t="n">
+        <v>409</v>
+      </c>
+      <c r="F34" t="n">
+        <v>412</v>
+      </c>
+      <c r="G34" t="n">
+        <v>411</v>
+      </c>
+      <c r="H34" t="n">
+        <v>431</v>
+      </c>
+      <c r="I34" t="n">
         <v>426</v>
       </c>
-      <c r="E34" t="n">
-        <v>392</v>
-      </c>
-      <c r="F34" t="n">
-        <v>431</v>
-      </c>
-      <c r="G34" t="n">
-        <v>443</v>
-      </c>
-      <c r="H34" t="n">
-        <v>438</v>
-      </c>
-      <c r="I34" t="n">
-        <v>387</v>
-      </c>
       <c r="J34" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K34" t="n">
-        <v>452</v>
+        <v>433</v>
       </c>
       <c r="L34" t="n">
-        <v>420.6</v>
+        <v>420.1</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>543</v>
+        <v>497</v>
       </c>
       <c r="C35" t="n">
-        <v>471</v>
+        <v>542</v>
       </c>
       <c r="D35" t="n">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="E35" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F35" t="n">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="G35" t="n">
-        <v>483</v>
+        <v>432</v>
       </c>
       <c r="H35" t="n">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="I35" t="n">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="J35" t="n">
-        <v>477</v>
+        <v>454</v>
       </c>
       <c r="K35" t="n">
-        <v>436</v>
+        <v>522</v>
       </c>
       <c r="L35" t="n">
-        <v>479.9</v>
+        <v>482.3</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="C36" t="n">
-        <v>391</v>
+        <v>329</v>
       </c>
       <c r="D36" t="n">
+        <v>351</v>
+      </c>
+      <c r="E36" t="n">
         <v>411</v>
       </c>
-      <c r="E36" t="n">
-        <v>391</v>
-      </c>
       <c r="F36" t="n">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="G36" t="n">
-        <v>355</v>
+        <v>395</v>
       </c>
       <c r="H36" t="n">
-        <v>425</v>
+        <v>393</v>
       </c>
       <c r="I36" t="n">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="J36" t="n">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="K36" t="n">
-        <v>403</v>
+        <v>439</v>
       </c>
       <c r="L36" t="n">
-        <v>386.7</v>
+        <v>384.6</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>518</v>
+        <v>415</v>
       </c>
       <c r="C37" t="n">
-        <v>461</v>
+        <v>422</v>
       </c>
       <c r="D37" t="n">
-        <v>401</v>
+        <v>440</v>
       </c>
       <c r="E37" t="n">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="F37" t="n">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="G37" t="n">
-        <v>469</v>
+        <v>448</v>
       </c>
       <c r="H37" t="n">
-        <v>439</v>
+        <v>418</v>
       </c>
       <c r="I37" t="n">
-        <v>460</v>
+        <v>418</v>
       </c>
       <c r="J37" t="n">
-        <v>394</v>
+        <v>459</v>
       </c>
       <c r="K37" t="n">
-        <v>478</v>
+        <v>397</v>
       </c>
       <c r="L37" t="n">
-        <v>452</v>
+        <v>429.3</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
+        <v>564</v>
+      </c>
+      <c r="C38" t="n">
+        <v>651</v>
+      </c>
+      <c r="D38" t="n">
+        <v>502</v>
+      </c>
+      <c r="E38" t="n">
+        <v>492</v>
+      </c>
+      <c r="F38" t="n">
         <v>535</v>
       </c>
-      <c r="C38" t="n">
-        <v>598</v>
-      </c>
-      <c r="D38" t="n">
-        <v>594</v>
-      </c>
-      <c r="E38" t="n">
-        <v>504</v>
-      </c>
-      <c r="F38" t="n">
-        <v>590</v>
-      </c>
       <c r="G38" t="n">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="H38" t="n">
-        <v>509</v>
+        <v>466</v>
       </c>
       <c r="I38" t="n">
-        <v>671</v>
+        <v>599</v>
       </c>
       <c r="J38" t="n">
-        <v>539</v>
+        <v>495</v>
       </c>
       <c r="K38" t="n">
-        <v>497</v>
+        <v>612</v>
       </c>
       <c r="L38" t="n">
-        <v>560.5</v>
+        <v>549.6</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="C39" t="n">
-        <v>444</v>
+        <v>375</v>
       </c>
       <c r="D39" t="n">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="E39" t="n">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="F39" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="G39" t="n">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="H39" t="n">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="I39" t="n">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="J39" t="n">
-        <v>426</v>
+        <v>398</v>
       </c>
       <c r="K39" t="n">
-        <v>367</v>
+        <v>438</v>
       </c>
       <c r="L39" t="n">
-        <v>410.7</v>
+        <v>401.8</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C40" t="n">
-        <v>459</v>
+        <v>416</v>
       </c>
       <c r="D40" t="n">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="E40" t="n">
-        <v>461</v>
+        <v>421</v>
       </c>
       <c r="F40" t="n">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="G40" t="n">
-        <v>448</v>
+        <v>513</v>
       </c>
       <c r="H40" t="n">
-        <v>435</v>
+        <v>503</v>
       </c>
       <c r="I40" t="n">
-        <v>461</v>
+        <v>507</v>
       </c>
       <c r="J40" t="n">
-        <v>469</v>
+        <v>449</v>
       </c>
       <c r="K40" t="n">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="L40" t="n">
-        <v>456.8</v>
+        <v>468.2</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>519</v>
+        <v>479</v>
       </c>
       <c r="C41" t="n">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="D41" t="n">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="E41" t="n">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F41" t="n">
-        <v>564</v>
+        <v>517</v>
       </c>
       <c r="G41" t="n">
-        <v>535</v>
+        <v>503</v>
       </c>
       <c r="H41" t="n">
-        <v>489</v>
+        <v>542</v>
       </c>
       <c r="I41" t="n">
-        <v>531</v>
+        <v>493</v>
       </c>
       <c r="J41" t="n">
-        <v>503</v>
+        <v>466</v>
       </c>
       <c r="K41" t="n">
-        <v>498</v>
+        <v>530</v>
       </c>
       <c r="L41" t="n">
-        <v>522.7</v>
+        <v>512.9</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="C42" t="n">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="D42" t="n">
-        <v>440</v>
+        <v>465</v>
       </c>
       <c r="E42" t="n">
-        <v>485</v>
+        <v>432</v>
       </c>
       <c r="F42" t="n">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="G42" t="n">
-        <v>504</v>
+        <v>437</v>
       </c>
       <c r="H42" t="n">
-        <v>512</v>
+        <v>449</v>
       </c>
       <c r="I42" t="n">
-        <v>495</v>
+        <v>368</v>
       </c>
       <c r="J42" t="n">
-        <v>467</v>
+        <v>435</v>
       </c>
       <c r="K42" t="n">
-        <v>473</v>
+        <v>398</v>
       </c>
       <c r="L42" t="n">
-        <v>483.1</v>
+        <v>443.7</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>424</v>
+        <v>474</v>
       </c>
       <c r="C43" t="n">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D43" t="n">
-        <v>477</v>
+        <v>443</v>
       </c>
       <c r="E43" t="n">
-        <v>471</v>
+        <v>442</v>
       </c>
       <c r="F43" t="n">
-        <v>484</v>
+        <v>528</v>
       </c>
       <c r="G43" t="n">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="H43" t="n">
-        <v>484</v>
+        <v>509</v>
       </c>
       <c r="I43" t="n">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="J43" t="n">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="K43" t="n">
-        <v>480</v>
+        <v>427</v>
       </c>
       <c r="L43" t="n">
-        <v>472.2</v>
+        <v>473.8</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>464</v>
+        <v>437</v>
       </c>
       <c r="C44" t="n">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="D44" t="n">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E44" t="n">
-        <v>414</v>
+        <v>457</v>
       </c>
       <c r="F44" t="n">
-        <v>397</v>
+        <v>431</v>
       </c>
       <c r="G44" t="n">
-        <v>432</v>
+        <v>411</v>
       </c>
       <c r="H44" t="n">
         <v>498</v>
       </c>
       <c r="I44" t="n">
-        <v>464</v>
+        <v>493</v>
       </c>
       <c r="J44" t="n">
-        <v>467</v>
+        <v>444</v>
       </c>
       <c r="K44" t="n">
-        <v>431</v>
+        <v>462</v>
       </c>
       <c r="L44" t="n">
-        <v>445.5</v>
+        <v>455.5</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>514</v>
+        <v>477</v>
       </c>
       <c r="C45" t="n">
-        <v>540</v>
+        <v>473</v>
       </c>
       <c r="D45" t="n">
-        <v>476</v>
+        <v>453</v>
       </c>
       <c r="E45" t="n">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="F45" t="n">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="G45" t="n">
-        <v>435</v>
+        <v>515</v>
       </c>
       <c r="H45" t="n">
-        <v>449</v>
+        <v>500</v>
       </c>
       <c r="I45" t="n">
-        <v>505</v>
+        <v>441</v>
       </c>
       <c r="J45" t="n">
         <v>446</v>
       </c>
       <c r="K45" t="n">
-        <v>421</v>
+        <v>495</v>
       </c>
       <c r="L45" t="n">
-        <v>472.2</v>
+        <v>470.7</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="C46" t="n">
-        <v>372</v>
+        <v>419</v>
       </c>
       <c r="D46" t="n">
-        <v>450</v>
+        <v>401</v>
       </c>
       <c r="E46" t="n">
-        <v>347</v>
+        <v>376</v>
       </c>
       <c r="F46" t="n">
-        <v>355</v>
+        <v>454</v>
       </c>
       <c r="G46" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="H46" t="n">
-        <v>412</v>
+        <v>446</v>
       </c>
       <c r="I46" t="n">
-        <v>432</v>
+        <v>340</v>
       </c>
       <c r="J46" t="n">
-        <v>393</v>
+        <v>358</v>
       </c>
       <c r="K46" t="n">
-        <v>395</v>
+        <v>451</v>
       </c>
       <c r="L46" t="n">
-        <v>402.1</v>
+        <v>408.7</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>463</v>
+        <v>572</v>
       </c>
       <c r="C47" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="D47" t="n">
-        <v>478</v>
+        <v>431</v>
       </c>
       <c r="E47" t="n">
-        <v>494</v>
+        <v>473</v>
       </c>
       <c r="F47" t="n">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="G47" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="H47" t="n">
-        <v>486</v>
+        <v>541</v>
       </c>
       <c r="I47" t="n">
-        <v>574</v>
+        <v>449</v>
       </c>
       <c r="J47" t="n">
-        <v>521</v>
+        <v>458</v>
       </c>
       <c r="K47" t="n">
-        <v>553</v>
+        <v>520</v>
       </c>
       <c r="L47" t="n">
-        <v>527.7</v>
+        <v>511.4</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>554</v>
+        <v>532</v>
       </c>
       <c r="C48" t="n">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="D48" t="n">
-        <v>462</v>
+        <v>493</v>
       </c>
       <c r="E48" t="n">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="F48" t="n">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="G48" t="n">
-        <v>607</v>
+        <v>513</v>
       </c>
       <c r="H48" t="n">
-        <v>529</v>
+        <v>502</v>
       </c>
       <c r="I48" t="n">
-        <v>455</v>
+        <v>526</v>
       </c>
       <c r="J48" t="n">
+        <v>543</v>
+      </c>
+      <c r="K48" t="n">
         <v>532</v>
       </c>
-      <c r="K48" t="n">
-        <v>492</v>
-      </c>
       <c r="L48" t="n">
-        <v>518</v>
+        <v>517.8</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C49" t="n">
-        <v>432</v>
+        <v>489</v>
       </c>
       <c r="D49" t="n">
-        <v>472</v>
+        <v>512</v>
       </c>
       <c r="E49" t="n">
-        <v>417</v>
+        <v>494</v>
       </c>
       <c r="F49" t="n">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="G49" t="n">
-        <v>472</v>
+        <v>434</v>
       </c>
       <c r="H49" t="n">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="I49" t="n">
+        <v>457</v>
+      </c>
+      <c r="J49" t="n">
+        <v>475</v>
+      </c>
+      <c r="K49" t="n">
         <v>470</v>
       </c>
-      <c r="J49" t="n">
-        <v>529</v>
-      </c>
-      <c r="K49" t="n">
-        <v>493</v>
-      </c>
       <c r="L49" t="n">
-        <v>472.1</v>
+        <v>472.2</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>403</v>
+        <v>436</v>
       </c>
       <c r="C50" t="n">
-        <v>447</v>
+        <v>415</v>
       </c>
       <c r="D50" t="n">
-        <v>503</v>
+        <v>474</v>
       </c>
       <c r="E50" t="n">
-        <v>476</v>
+        <v>448</v>
       </c>
       <c r="F50" t="n">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="G50" t="n">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="H50" t="n">
-        <v>456</v>
+        <v>426</v>
       </c>
       <c r="I50" t="n">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="J50" t="n">
-        <v>403</v>
+        <v>472</v>
       </c>
       <c r="K50" t="n">
-        <v>460</v>
+        <v>559</v>
       </c>
       <c r="L50" t="n">
-        <v>450</v>
+        <v>455.2</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C51" t="n">
-        <v>403</v>
+        <v>443</v>
       </c>
       <c r="D51" t="n">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="E51" t="n">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="F51" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G51" t="n">
-        <v>431</v>
+        <v>395</v>
       </c>
       <c r="H51" t="n">
-        <v>452</v>
+        <v>430</v>
       </c>
       <c r="I51" t="n">
-        <v>429</v>
+        <v>391</v>
       </c>
       <c r="J51" t="n">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="K51" t="n">
-        <v>459</v>
+        <v>423</v>
       </c>
       <c r="L51" t="n">
-        <v>439.9</v>
+        <v>432.4</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>469.74</v>
+        <v>461.8</v>
       </c>
       <c r="C52" t="n">
-        <v>459.96</v>
+        <v>469.7</v>
       </c>
       <c r="D52" t="n">
-        <v>472.52</v>
+        <v>464.32</v>
       </c>
       <c r="E52" t="n">
+        <v>457.46</v>
+      </c>
+      <c r="F52" t="n">
+        <v>464.84</v>
+      </c>
+      <c r="G52" t="n">
+        <v>464.82</v>
+      </c>
+      <c r="H52" t="n">
+        <v>464.38</v>
+      </c>
+      <c r="I52" t="n">
         <v>460.08</v>
       </c>
-      <c r="F52" t="n">
-        <v>473.3</v>
-      </c>
-      <c r="G52" t="n">
-        <v>472.42</v>
-      </c>
-      <c r="H52" t="n">
-        <v>465.34</v>
-      </c>
-      <c r="I52" t="n">
-        <v>472.56</v>
-      </c>
       <c r="J52" t="n">
-        <v>462.74</v>
+        <v>459.14</v>
       </c>
       <c r="K52" t="n">
-        <v>466.54</v>
+        <v>470.48</v>
       </c>
       <c r="L52" t="n">
-        <v>467.5200000000001</v>
+        <v>463.7020000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.801672458648682</v>
+        <v>2.342910289764404</v>
       </c>
       <c r="C2" t="n">
-        <v>2.500746726989746</v>
+        <v>2.411644458770752</v>
       </c>
       <c r="D2" t="n">
-        <v>2.521129608154297</v>
+        <v>2.314859628677368</v>
       </c>
       <c r="E2" t="n">
-        <v>2.585830926895142</v>
+        <v>2.355775594711304</v>
       </c>
       <c r="F2" t="n">
-        <v>2.453977108001709</v>
+        <v>2.366080522537231</v>
       </c>
       <c r="G2" t="n">
-        <v>2.373462438583374</v>
+        <v>2.390286922454834</v>
       </c>
       <c r="H2" t="n">
-        <v>2.252983570098877</v>
+        <v>2.364491939544678</v>
       </c>
       <c r="I2" t="n">
-        <v>2.408168792724609</v>
+        <v>2.374121189117432</v>
       </c>
       <c r="J2" t="n">
-        <v>2.397525072097778</v>
+        <v>2.438627004623413</v>
       </c>
       <c r="K2" t="n">
-        <v>2.61234450340271</v>
+        <v>2.367436170578003</v>
       </c>
       <c r="L2" t="n">
-        <v>2.490784120559693</v>
+        <v>2.372623372077942</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>2.643483400344849</v>
+        <v>2.730190515518188</v>
       </c>
       <c r="C3" t="n">
-        <v>2.540410757064819</v>
+        <v>2.597814798355103</v>
       </c>
       <c r="D3" t="n">
-        <v>2.622662544250488</v>
+        <v>3.056839466094971</v>
       </c>
       <c r="E3" t="n">
-        <v>2.619846105575562</v>
+        <v>2.7014319896698</v>
       </c>
       <c r="F3" t="n">
-        <v>2.735846281051636</v>
+        <v>2.533981323242188</v>
       </c>
       <c r="G3" t="n">
-        <v>2.626542806625366</v>
+        <v>2.639612913131714</v>
       </c>
       <c r="H3" t="n">
-        <v>2.749439477920532</v>
+        <v>2.827202081680298</v>
       </c>
       <c r="I3" t="n">
-        <v>2.954052686691284</v>
+        <v>2.575683355331421</v>
       </c>
       <c r="J3" t="n">
-        <v>2.889974355697632</v>
+        <v>3.345868110656738</v>
       </c>
       <c r="K3" t="n">
-        <v>2.57558798789978</v>
+        <v>2.547220468521118</v>
       </c>
       <c r="L3" t="n">
-        <v>2.695784640312195</v>
+        <v>2.755584502220154</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>2.699445962905884</v>
+        <v>4.010250329971313</v>
       </c>
       <c r="C4" t="n">
-        <v>2.571795225143433</v>
+        <v>2.603397130966187</v>
       </c>
       <c r="D4" t="n">
-        <v>2.916243076324463</v>
+        <v>2.681529521942139</v>
       </c>
       <c r="E4" t="n">
-        <v>2.46471118927002</v>
+        <v>2.654821157455444</v>
       </c>
       <c r="F4" t="n">
-        <v>2.494107723236084</v>
+        <v>3.349618196487427</v>
       </c>
       <c r="G4" t="n">
-        <v>2.611196756362915</v>
+        <v>2.907652616500854</v>
       </c>
       <c r="H4" t="n">
-        <v>2.626635074615479</v>
+        <v>3.736470222473145</v>
       </c>
       <c r="I4" t="n">
-        <v>2.555841207504272</v>
+        <v>2.730546951293945</v>
       </c>
       <c r="J4" t="n">
-        <v>2.353603839874268</v>
+        <v>2.609640598297119</v>
       </c>
       <c r="K4" t="n">
-        <v>2.511866807937622</v>
+        <v>2.689007759094238</v>
       </c>
       <c r="L4" t="n">
-        <v>2.580544686317444</v>
+        <v>2.997293448448181</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>2.1518714427948</v>
+        <v>2.20168137550354</v>
       </c>
       <c r="C5" t="n">
-        <v>2.255403518676758</v>
+        <v>2.306660175323486</v>
       </c>
       <c r="D5" t="n">
-        <v>2.254114627838135</v>
+        <v>2.285893440246582</v>
       </c>
       <c r="E5" t="n">
-        <v>2.242321729660034</v>
+        <v>2.471453428268433</v>
       </c>
       <c r="F5" t="n">
-        <v>2.256620407104492</v>
+        <v>2.306662797927856</v>
       </c>
       <c r="G5" t="n">
-        <v>2.259963750839233</v>
+        <v>2.276846647262573</v>
       </c>
       <c r="H5" t="n">
-        <v>2.372729301452637</v>
+        <v>3.044189929962158</v>
       </c>
       <c r="I5" t="n">
-        <v>2.426274299621582</v>
+        <v>2.798149585723877</v>
       </c>
       <c r="J5" t="n">
-        <v>2.477898836135864</v>
+        <v>2.474755764007568</v>
       </c>
       <c r="K5" t="n">
-        <v>2.984892845153809</v>
+        <v>2.368773221969604</v>
       </c>
       <c r="L5" t="n">
-        <v>2.368209075927735</v>
+        <v>2.453506636619568</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>2.207919120788574</v>
+        <v>2.599753618240356</v>
       </c>
       <c r="C6" t="n">
-        <v>2.227927684783936</v>
+        <v>2.331945180892944</v>
       </c>
       <c r="D6" t="n">
-        <v>2.20464015007019</v>
+        <v>2.389482736587524</v>
       </c>
       <c r="E6" t="n">
-        <v>2.214567184448242</v>
+        <v>2.107537031173706</v>
       </c>
       <c r="F6" t="n">
-        <v>2.995646476745605</v>
+        <v>2.08102011680603</v>
       </c>
       <c r="G6" t="n">
-        <v>2.563750982284546</v>
+        <v>2.111100673675537</v>
       </c>
       <c r="H6" t="n">
-        <v>2.554355144500732</v>
+        <v>2.757925748825073</v>
       </c>
       <c r="I6" t="n">
-        <v>2.397850513458252</v>
+        <v>2.519363403320312</v>
       </c>
       <c r="J6" t="n">
-        <v>2.142846584320068</v>
+        <v>2.07256817817688</v>
       </c>
       <c r="K6" t="n">
-        <v>2.354033708572388</v>
+        <v>2.142001867294312</v>
       </c>
       <c r="L6" t="n">
-        <v>2.386353754997253</v>
+        <v>2.311269855499268</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>2.684610843658447</v>
+        <v>2.16456937789917</v>
       </c>
       <c r="C7" t="n">
-        <v>2.767860174179077</v>
+        <v>2.275570869445801</v>
       </c>
       <c r="D7" t="n">
-        <v>2.678239583969116</v>
+        <v>2.294026613235474</v>
       </c>
       <c r="E7" t="n">
-        <v>2.665642499923706</v>
+        <v>2.457520484924316</v>
       </c>
       <c r="F7" t="n">
-        <v>2.561974048614502</v>
+        <v>2.264524459838867</v>
       </c>
       <c r="G7" t="n">
-        <v>2.551122665405273</v>
+        <v>2.480266332626343</v>
       </c>
       <c r="H7" t="n">
-        <v>2.652446746826172</v>
+        <v>2.297621965408325</v>
       </c>
       <c r="I7" t="n">
-        <v>2.782377958297729</v>
+        <v>2.424321174621582</v>
       </c>
       <c r="J7" t="n">
-        <v>2.599011421203613</v>
+        <v>2.440101385116577</v>
       </c>
       <c r="K7" t="n">
-        <v>2.625157594680786</v>
+        <v>2.546956300735474</v>
       </c>
       <c r="L7" t="n">
-        <v>2.656844353675842</v>
+        <v>2.364547896385193</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>2.698550224304199</v>
+        <v>2.457014560699463</v>
       </c>
       <c r="C8" t="n">
-        <v>2.732797622680664</v>
+        <v>2.305514574050903</v>
       </c>
       <c r="D8" t="n">
-        <v>2.834726333618164</v>
+        <v>2.512107133865356</v>
       </c>
       <c r="E8" t="n">
-        <v>2.436160326004028</v>
+        <v>2.497504234313965</v>
       </c>
       <c r="F8" t="n">
-        <v>2.483681440353394</v>
+        <v>2.314949035644531</v>
       </c>
       <c r="G8" t="n">
-        <v>2.450965166091919</v>
+        <v>2.358033180236816</v>
       </c>
       <c r="H8" t="n">
-        <v>2.527052402496338</v>
+        <v>2.796994686126709</v>
       </c>
       <c r="I8" t="n">
-        <v>2.592252731323242</v>
+        <v>2.568406581878662</v>
       </c>
       <c r="J8" t="n">
-        <v>2.549243688583374</v>
+        <v>2.469245433807373</v>
       </c>
       <c r="K8" t="n">
-        <v>2.57950496673584</v>
+        <v>2.274763345718384</v>
       </c>
       <c r="L8" t="n">
-        <v>2.588493490219116</v>
+        <v>2.455453276634216</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>2.565533876419067</v>
+        <v>2.365608215332031</v>
       </c>
       <c r="C9" t="n">
-        <v>2.523475646972656</v>
+        <v>2.610684394836426</v>
       </c>
       <c r="D9" t="n">
-        <v>2.603129386901855</v>
+        <v>2.213277339935303</v>
       </c>
       <c r="E9" t="n">
-        <v>2.573084831237793</v>
+        <v>2.122575759887695</v>
       </c>
       <c r="F9" t="n">
-        <v>2.452472448348999</v>
+        <v>2.182327032089233</v>
       </c>
       <c r="G9" t="n">
-        <v>2.594866752624512</v>
+        <v>2.14535117149353</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4460129737854</v>
+        <v>2.171799659729004</v>
       </c>
       <c r="I9" t="n">
-        <v>2.302816390991211</v>
+        <v>2.243156433105469</v>
       </c>
       <c r="J9" t="n">
-        <v>2.317633152008057</v>
+        <v>2.271152973175049</v>
       </c>
       <c r="K9" t="n">
-        <v>2.265767335891724</v>
+        <v>2.349706649780273</v>
       </c>
       <c r="L9" t="n">
-        <v>2.464479279518128</v>
+        <v>2.267563962936401</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>2.436192035675049</v>
+        <v>1.992042303085327</v>
       </c>
       <c r="C10" t="n">
-        <v>2.380462646484375</v>
+        <v>2.063103675842285</v>
       </c>
       <c r="D10" t="n">
-        <v>2.284932136535645</v>
+        <v>2.237536430358887</v>
       </c>
       <c r="E10" t="n">
-        <v>2.157590866088867</v>
+        <v>2.192920446395874</v>
       </c>
       <c r="F10" t="n">
-        <v>2.426438331604004</v>
+        <v>2.464243412017822</v>
       </c>
       <c r="G10" t="n">
-        <v>2.283174991607666</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H10" t="n">
-        <v>2.338396787643433</v>
+        <v>2.159206867218018</v>
       </c>
       <c r="I10" t="n">
-        <v>2.227596282958984</v>
+        <v>2.473002433776855</v>
       </c>
       <c r="J10" t="n">
-        <v>2.496821641921997</v>
+        <v>2.4129319190979</v>
       </c>
       <c r="K10" t="n">
-        <v>2.465484380722046</v>
+        <v>2.165192604064941</v>
       </c>
       <c r="L10" t="n">
-        <v>2.349709010124207</v>
+        <v>2.238061785697937</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1.905625820159912</v>
+        <v>1.8444504737854</v>
       </c>
       <c r="C11" t="n">
-        <v>1.971133947372437</v>
+        <v>1.85570216178894</v>
       </c>
       <c r="D11" t="n">
-        <v>1.994064807891846</v>
+        <v>1.834300756454468</v>
       </c>
       <c r="E11" t="n">
-        <v>1.923812866210938</v>
+        <v>1.970995426177979</v>
       </c>
       <c r="F11" t="n">
-        <v>1.924145936965942</v>
+        <v>1.929043292999268</v>
       </c>
       <c r="G11" t="n">
-        <v>1.934382438659668</v>
+        <v>1.828435659408569</v>
       </c>
       <c r="H11" t="n">
-        <v>2.069631099700928</v>
+        <v>1.896183013916016</v>
       </c>
       <c r="I11" t="n">
-        <v>1.963146209716797</v>
+        <v>1.883682727813721</v>
       </c>
       <c r="J11" t="n">
-        <v>1.994479417800903</v>
+        <v>1.883323431015015</v>
       </c>
       <c r="K11" t="n">
-        <v>1.962090730667114</v>
+        <v>1.936797618865967</v>
       </c>
       <c r="L11" t="n">
-        <v>1.964251327514648</v>
+        <v>1.886291456222534</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>2.263895511627197</v>
+        <v>2.223577260971069</v>
       </c>
       <c r="C12" t="n">
-        <v>2.146187543869019</v>
+        <v>2.157021999359131</v>
       </c>
       <c r="D12" t="n">
-        <v>2.238967180252075</v>
+        <v>2.213894128799438</v>
       </c>
       <c r="E12" t="n">
-        <v>2.245705127716064</v>
+        <v>2.202622890472412</v>
       </c>
       <c r="F12" t="n">
-        <v>2.308624267578125</v>
+        <v>2.185009717941284</v>
       </c>
       <c r="G12" t="n">
-        <v>2.344915866851807</v>
+        <v>2.21934175491333</v>
       </c>
       <c r="H12" t="n">
-        <v>2.264129638671875</v>
+        <v>2.19680643081665</v>
       </c>
       <c r="I12" t="n">
-        <v>2.408936738967896</v>
+        <v>2.137810468673706</v>
       </c>
       <c r="J12" t="n">
-        <v>2.298921823501587</v>
+        <v>2.159952878952026</v>
       </c>
       <c r="K12" t="n">
-        <v>2.339730501174927</v>
+        <v>2.31413745880127</v>
       </c>
       <c r="L12" t="n">
-        <v>2.286001420021057</v>
+        <v>2.201017498970032</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>2.227372169494629</v>
+        <v>2.124884366989136</v>
       </c>
       <c r="C13" t="n">
-        <v>2.203374624252319</v>
+        <v>2.489194631576538</v>
       </c>
       <c r="D13" t="n">
-        <v>2.432749271392822</v>
+        <v>2.281285285949707</v>
       </c>
       <c r="E13" t="n">
-        <v>2.391459465026855</v>
+        <v>2.40364933013916</v>
       </c>
       <c r="F13" t="n">
-        <v>2.562612533569336</v>
+        <v>2.135987043380737</v>
       </c>
       <c r="G13" t="n">
-        <v>2.238179445266724</v>
+        <v>2.056318998336792</v>
       </c>
       <c r="H13" t="n">
-        <v>2.252047300338745</v>
+        <v>2.089320421218872</v>
       </c>
       <c r="I13" t="n">
-        <v>2.276917934417725</v>
+        <v>2.190237998962402</v>
       </c>
       <c r="J13" t="n">
-        <v>2.373431444168091</v>
+        <v>2.111912488937378</v>
       </c>
       <c r="K13" t="n">
-        <v>2.198471546173096</v>
+        <v>2.074498176574707</v>
       </c>
       <c r="L13" t="n">
-        <v>2.315661573410034</v>
+        <v>2.195728874206543</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>2.326151132583618</v>
+        <v>2.180987119674683</v>
       </c>
       <c r="C14" t="n">
-        <v>2.25608491897583</v>
+        <v>2.476776838302612</v>
       </c>
       <c r="D14" t="n">
-        <v>2.569233417510986</v>
+        <v>2.402077913284302</v>
       </c>
       <c r="E14" t="n">
-        <v>2.664244651794434</v>
+        <v>2.374157428741455</v>
       </c>
       <c r="F14" t="n">
-        <v>2.445377111434937</v>
+        <v>2.244327783584595</v>
       </c>
       <c r="G14" t="n">
-        <v>2.442761421203613</v>
+        <v>2.256298542022705</v>
       </c>
       <c r="H14" t="n">
-        <v>2.418918132781982</v>
+        <v>2.376431465148926</v>
       </c>
       <c r="I14" t="n">
-        <v>2.294193267822266</v>
+        <v>2.474760055541992</v>
       </c>
       <c r="J14" t="n">
-        <v>2.462777853012085</v>
+        <v>2.28535270690918</v>
       </c>
       <c r="K14" t="n">
-        <v>2.26173996925354</v>
+        <v>2.284627676010132</v>
       </c>
       <c r="L14" t="n">
-        <v>2.414148187637329</v>
+        <v>2.335579752922058</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>2.240641117095947</v>
+        <v>2.119338750839233</v>
       </c>
       <c r="C15" t="n">
-        <v>2.215563535690308</v>
+        <v>2.251796007156372</v>
       </c>
       <c r="D15" t="n">
-        <v>2.398000001907349</v>
+        <v>2.136342525482178</v>
       </c>
       <c r="E15" t="n">
-        <v>2.402312040328979</v>
+        <v>2.11389946937561</v>
       </c>
       <c r="F15" t="n">
-        <v>2.295142650604248</v>
+        <v>2.100780248641968</v>
       </c>
       <c r="G15" t="n">
-        <v>2.331234455108643</v>
+        <v>2.207159042358398</v>
       </c>
       <c r="H15" t="n">
-        <v>2.229325771331787</v>
+        <v>2.110840082168579</v>
       </c>
       <c r="I15" t="n">
-        <v>2.272514581680298</v>
+        <v>2.199273824691772</v>
       </c>
       <c r="J15" t="n">
-        <v>2.257423877716064</v>
+        <v>2.031331300735474</v>
       </c>
       <c r="K15" t="n">
-        <v>2.399846315383911</v>
+        <v>2.356916666030884</v>
       </c>
       <c r="L15" t="n">
-        <v>2.304200434684753</v>
+        <v>2.162767791748047</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>2.439496517181396</v>
+        <v>2.350358963012695</v>
       </c>
       <c r="C16" t="n">
-        <v>2.338064670562744</v>
+        <v>2.353144884109497</v>
       </c>
       <c r="D16" t="n">
-        <v>2.341274976730347</v>
+        <v>2.273277759552002</v>
       </c>
       <c r="E16" t="n">
-        <v>2.336382865905762</v>
+        <v>2.248602867126465</v>
       </c>
       <c r="F16" t="n">
-        <v>2.485639333724976</v>
+        <v>2.29414701461792</v>
       </c>
       <c r="G16" t="n">
-        <v>2.413105249404907</v>
+        <v>2.387983560562134</v>
       </c>
       <c r="H16" t="n">
-        <v>2.439505338668823</v>
+        <v>2.334839344024658</v>
       </c>
       <c r="I16" t="n">
-        <v>2.334262609481812</v>
+        <v>2.229703903198242</v>
       </c>
       <c r="J16" t="n">
-        <v>2.559266567230225</v>
+        <v>2.218783140182495</v>
       </c>
       <c r="K16" t="n">
-        <v>2.393065214157104</v>
+        <v>2.281710147857666</v>
       </c>
       <c r="L16" t="n">
-        <v>2.408006334304809</v>
+        <v>2.297255158424377</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>2.443184852600098</v>
+        <v>2.119945764541626</v>
       </c>
       <c r="C17" t="n">
-        <v>2.388854742050171</v>
+        <v>2.117246866226196</v>
       </c>
       <c r="D17" t="n">
-        <v>2.292999029159546</v>
+        <v>2.256356716156006</v>
       </c>
       <c r="E17" t="n">
-        <v>2.260900020599365</v>
+        <v>2.359363317489624</v>
       </c>
       <c r="F17" t="n">
-        <v>2.186016321182251</v>
+        <v>2.373979568481445</v>
       </c>
       <c r="G17" t="n">
-        <v>2.344078779220581</v>
+        <v>2.22199821472168</v>
       </c>
       <c r="H17" t="n">
-        <v>2.232295751571655</v>
+        <v>2.197085618972778</v>
       </c>
       <c r="I17" t="n">
-        <v>2.177778482437134</v>
+        <v>2.055522918701172</v>
       </c>
       <c r="J17" t="n">
-        <v>2.48707914352417</v>
+        <v>2.149027585983276</v>
       </c>
       <c r="K17" t="n">
-        <v>2.393895626068115</v>
+        <v>2.197938680648804</v>
       </c>
       <c r="L17" t="n">
-        <v>2.320708274841309</v>
+        <v>2.204846525192261</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>2.480144500732422</v>
+        <v>2.268308639526367</v>
       </c>
       <c r="C18" t="n">
-        <v>2.404239177703857</v>
+        <v>2.606862306594849</v>
       </c>
       <c r="D18" t="n">
-        <v>2.708224773406982</v>
+        <v>2.341070413589478</v>
       </c>
       <c r="E18" t="n">
-        <v>2.397580862045288</v>
+        <v>2.342421770095825</v>
       </c>
       <c r="F18" t="n">
-        <v>2.912504434585571</v>
+        <v>2.326703786849976</v>
       </c>
       <c r="G18" t="n">
-        <v>2.480105876922607</v>
+        <v>2.545593738555908</v>
       </c>
       <c r="H18" t="n">
-        <v>2.564824819564819</v>
+        <v>2.416592121124268</v>
       </c>
       <c r="I18" t="n">
-        <v>2.593119621276855</v>
+        <v>2.485300540924072</v>
       </c>
       <c r="J18" t="n">
-        <v>2.507736682891846</v>
+        <v>2.451816082000732</v>
       </c>
       <c r="K18" t="n">
-        <v>2.440549373626709</v>
+        <v>2.593259572982788</v>
       </c>
       <c r="L18" t="n">
-        <v>2.548903012275696</v>
+        <v>2.437792897224426</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>2.182312250137329</v>
+        <v>2.148334264755249</v>
       </c>
       <c r="C19" t="n">
-        <v>2.235194683074951</v>
+        <v>2.226855278015137</v>
       </c>
       <c r="D19" t="n">
-        <v>2.149852275848389</v>
+        <v>2.18816351890564</v>
       </c>
       <c r="E19" t="n">
-        <v>2.229804039001465</v>
+        <v>2.10814905166626</v>
       </c>
       <c r="F19" t="n">
-        <v>2.601292133331299</v>
+        <v>2.073163509368896</v>
       </c>
       <c r="G19" t="n">
-        <v>2.205740451812744</v>
+        <v>2.292590618133545</v>
       </c>
       <c r="H19" t="n">
-        <v>2.222699880599976</v>
+        <v>2.234616756439209</v>
       </c>
       <c r="I19" t="n">
-        <v>2.233556985855103</v>
+        <v>2.132808685302734</v>
       </c>
       <c r="J19" t="n">
-        <v>2.546597003936768</v>
+        <v>2.185598850250244</v>
       </c>
       <c r="K19" t="n">
-        <v>2.22941780090332</v>
+        <v>2.329201936721802</v>
       </c>
       <c r="L19" t="n">
-        <v>2.283646750450134</v>
+        <v>2.191948246955872</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>2.207176208496094</v>
+        <v>2.334610223770142</v>
       </c>
       <c r="C20" t="n">
-        <v>2.599927186965942</v>
+        <v>2.247043371200562</v>
       </c>
       <c r="D20" t="n">
-        <v>2.320709228515625</v>
+        <v>2.218471050262451</v>
       </c>
       <c r="E20" t="n">
-        <v>2.371189117431641</v>
+        <v>2.189110279083252</v>
       </c>
       <c r="F20" t="n">
-        <v>2.20859169960022</v>
+        <v>2.224503993988037</v>
       </c>
       <c r="G20" t="n">
-        <v>2.309470415115356</v>
+        <v>2.111936092376709</v>
       </c>
       <c r="H20" t="n">
-        <v>2.447634696960449</v>
+        <v>2.303027868270874</v>
       </c>
       <c r="I20" t="n">
-        <v>2.35451340675354</v>
+        <v>2.136592149734497</v>
       </c>
       <c r="J20" t="n">
-        <v>2.703508138656616</v>
+        <v>2.423489570617676</v>
       </c>
       <c r="K20" t="n">
-        <v>2.445420026779175</v>
+        <v>2.309703826904297</v>
       </c>
       <c r="L20" t="n">
-        <v>2.396814012527466</v>
+        <v>2.24984884262085</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>2.473838806152344</v>
+        <v>2.53188419342041</v>
       </c>
       <c r="C21" t="n">
-        <v>2.42289662361145</v>
+        <v>2.426551580429077</v>
       </c>
       <c r="D21" t="n">
-        <v>2.505196094512939</v>
+        <v>2.444364309310913</v>
       </c>
       <c r="E21" t="n">
-        <v>2.287028074264526</v>
+        <v>2.22709584236145</v>
       </c>
       <c r="F21" t="n">
-        <v>2.432052373886108</v>
+        <v>2.686013698577881</v>
       </c>
       <c r="G21" t="n">
-        <v>2.438578844070435</v>
+        <v>3.623317718505859</v>
       </c>
       <c r="H21" t="n">
-        <v>2.286418437957764</v>
+        <v>2.167589426040649</v>
       </c>
       <c r="I21" t="n">
-        <v>2.381526708602905</v>
+        <v>2.267360210418701</v>
       </c>
       <c r="J21" t="n">
-        <v>2.446970701217651</v>
+        <v>2.325958728790283</v>
       </c>
       <c r="K21" t="n">
-        <v>2.259718656539917</v>
+        <v>2.420062065124512</v>
       </c>
       <c r="L21" t="n">
-        <v>2.393422532081604</v>
+        <v>2.512019777297974</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>2.234708309173584</v>
+        <v>2.184897184371948</v>
       </c>
       <c r="C22" t="n">
-        <v>2.245689153671265</v>
+        <v>2.228106737136841</v>
       </c>
       <c r="D22" t="n">
-        <v>2.211081027984619</v>
+        <v>2.163037538528442</v>
       </c>
       <c r="E22" t="n">
-        <v>2.155013561248779</v>
+        <v>2.211052179336548</v>
       </c>
       <c r="F22" t="n">
-        <v>2.282265901565552</v>
+        <v>2.235458135604858</v>
       </c>
       <c r="G22" t="n">
-        <v>2.204115867614746</v>
+        <v>2.195058345794678</v>
       </c>
       <c r="H22" t="n">
-        <v>2.284016132354736</v>
+        <v>2.248422622680664</v>
       </c>
       <c r="I22" t="n">
-        <v>2.280375957489014</v>
+        <v>2.062109470367432</v>
       </c>
       <c r="J22" t="n">
-        <v>2.422199010848999</v>
+        <v>2.305085420608521</v>
       </c>
       <c r="K22" t="n">
-        <v>2.354986667633057</v>
+        <v>2.170616149902344</v>
       </c>
       <c r="L22" t="n">
-        <v>2.267445158958435</v>
+        <v>2.200384378433228</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1.938132047653198</v>
+        <v>1.970014333724976</v>
       </c>
       <c r="C23" t="n">
-        <v>2.058018922805786</v>
+        <v>1.940225839614868</v>
       </c>
       <c r="D23" t="n">
-        <v>2.02087140083313</v>
+        <v>1.954278230667114</v>
       </c>
       <c r="E23" t="n">
-        <v>2.044909000396729</v>
+        <v>2.133101224899292</v>
       </c>
       <c r="F23" t="n">
-        <v>2.047064304351807</v>
+        <v>1.973669290542603</v>
       </c>
       <c r="G23" t="n">
-        <v>2.048134803771973</v>
+        <v>1.935873031616211</v>
       </c>
       <c r="H23" t="n">
-        <v>2.02836799621582</v>
+        <v>1.946503400802612</v>
       </c>
       <c r="I23" t="n">
-        <v>2.165990591049194</v>
+        <v>1.983853578567505</v>
       </c>
       <c r="J23" t="n">
-        <v>2.093525886535645</v>
+        <v>2.231191158294678</v>
       </c>
       <c r="K23" t="n">
-        <v>1.998771667480469</v>
+        <v>2.114359617233276</v>
       </c>
       <c r="L23" t="n">
-        <v>2.044378662109375</v>
+        <v>2.018306970596313</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>2.135355234146118</v>
+        <v>2.046725988388062</v>
       </c>
       <c r="C24" t="n">
-        <v>1.972739934921265</v>
+        <v>2.260905265808105</v>
       </c>
       <c r="D24" t="n">
-        <v>2.157983541488647</v>
+        <v>1.922247886657715</v>
       </c>
       <c r="E24" t="n">
-        <v>2.045131206512451</v>
+        <v>2.077275514602661</v>
       </c>
       <c r="F24" t="n">
-        <v>2.027674198150635</v>
+        <v>1.958409786224365</v>
       </c>
       <c r="G24" t="n">
-        <v>2.159420967102051</v>
+        <v>1.932589769363403</v>
       </c>
       <c r="H24" t="n">
-        <v>2.102991104125977</v>
+        <v>2.05510401725769</v>
       </c>
       <c r="I24" t="n">
-        <v>2.120084524154663</v>
+        <v>2.049782514572144</v>
       </c>
       <c r="J24" t="n">
-        <v>2.043393850326538</v>
+        <v>2.004030704498291</v>
       </c>
       <c r="K24" t="n">
-        <v>2.103240251541138</v>
+        <v>2.018077373504639</v>
       </c>
       <c r="L24" t="n">
-        <v>2.086801481246948</v>
+        <v>2.032514882087708</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>2.376266002655029</v>
+        <v>2.083129405975342</v>
       </c>
       <c r="C25" t="n">
-        <v>2.114690542221069</v>
+        <v>2.093276262283325</v>
       </c>
       <c r="D25" t="n">
-        <v>2.198061943054199</v>
+        <v>2.096081972122192</v>
       </c>
       <c r="E25" t="n">
-        <v>2.138814687728882</v>
+        <v>2.290940999984741</v>
       </c>
       <c r="F25" t="n">
-        <v>2.14337158203125</v>
+        <v>2.106295347213745</v>
       </c>
       <c r="G25" t="n">
-        <v>2.265727519989014</v>
+        <v>2.029081344604492</v>
       </c>
       <c r="H25" t="n">
-        <v>2.221814632415771</v>
+        <v>2.063703298568726</v>
       </c>
       <c r="I25" t="n">
-        <v>2.35341477394104</v>
+        <v>2.152843236923218</v>
       </c>
       <c r="J25" t="n">
-        <v>2.23212194442749</v>
+        <v>2.071435451507568</v>
       </c>
       <c r="K25" t="n">
-        <v>2.13782525062561</v>
+        <v>2.395451068878174</v>
       </c>
       <c r="L25" t="n">
-        <v>2.218210887908936</v>
+        <v>2.138223838806153</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>2.566620588302612</v>
+        <v>2.423864841461182</v>
       </c>
       <c r="C26" t="n">
-        <v>2.404801368713379</v>
+        <v>2.303512573242188</v>
       </c>
       <c r="D26" t="n">
-        <v>2.489768505096436</v>
+        <v>2.430410623550415</v>
       </c>
       <c r="E26" t="n">
-        <v>2.489549875259399</v>
+        <v>2.465165376663208</v>
       </c>
       <c r="F26" t="n">
-        <v>2.444923877716064</v>
+        <v>2.45894193649292</v>
       </c>
       <c r="G26" t="n">
-        <v>2.394557476043701</v>
+        <v>2.453582525253296</v>
       </c>
       <c r="H26" t="n">
-        <v>2.366886854171753</v>
+        <v>2.75406551361084</v>
       </c>
       <c r="I26" t="n">
-        <v>2.467902421951294</v>
+        <v>2.309370040893555</v>
       </c>
       <c r="J26" t="n">
-        <v>2.703633308410645</v>
+        <v>2.261636257171631</v>
       </c>
       <c r="K26" t="n">
-        <v>2.87014365196228</v>
+        <v>2.514497518539429</v>
       </c>
       <c r="L26" t="n">
-        <v>2.519878792762756</v>
+        <v>2.437504720687866</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>2.44254469871521</v>
+        <v>2.047731399536133</v>
       </c>
       <c r="C27" t="n">
-        <v>2.31879734992981</v>
+        <v>2.186418771743774</v>
       </c>
       <c r="D27" t="n">
-        <v>2.386415004730225</v>
+        <v>2.171518325805664</v>
       </c>
       <c r="E27" t="n">
-        <v>2.227871894836426</v>
+        <v>2.192846775054932</v>
       </c>
       <c r="F27" t="n">
-        <v>2.369063854217529</v>
+        <v>1.966687917709351</v>
       </c>
       <c r="G27" t="n">
-        <v>2.124257802963257</v>
+        <v>2.113149881362915</v>
       </c>
       <c r="H27" t="n">
-        <v>2.345690250396729</v>
+        <v>2.100070953369141</v>
       </c>
       <c r="I27" t="n">
-        <v>2.462924718856812</v>
+        <v>2.166246652603149</v>
       </c>
       <c r="J27" t="n">
-        <v>2.093175172805786</v>
+        <v>2.265923261642456</v>
       </c>
       <c r="K27" t="n">
-        <v>2.372339963912964</v>
+        <v>2.135696649551392</v>
       </c>
       <c r="L27" t="n">
-        <v>2.314308071136475</v>
+        <v>2.13462905883789</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>2.215806245803833</v>
+        <v>2.009732484817505</v>
       </c>
       <c r="C28" t="n">
-        <v>2.25429105758667</v>
+        <v>2.103907346725464</v>
       </c>
       <c r="D28" t="n">
-        <v>2.422338247299194</v>
+        <v>1.948471307754517</v>
       </c>
       <c r="E28" t="n">
-        <v>2.23855185508728</v>
+        <v>2.067023754119873</v>
       </c>
       <c r="F28" t="n">
-        <v>2.106442928314209</v>
+        <v>2.057240724563599</v>
       </c>
       <c r="G28" t="n">
-        <v>2.28123664855957</v>
+        <v>2.128213167190552</v>
       </c>
       <c r="H28" t="n">
-        <v>2.231427669525146</v>
+        <v>2.037103652954102</v>
       </c>
       <c r="I28" t="n">
-        <v>2.169317007064819</v>
+        <v>2.043400526046753</v>
       </c>
       <c r="J28" t="n">
-        <v>2.2508704662323</v>
+        <v>2.030515432357788</v>
       </c>
       <c r="K28" t="n">
-        <v>2.217077255249023</v>
+        <v>2.00938868522644</v>
       </c>
       <c r="L28" t="n">
-        <v>2.238735938072205</v>
+        <v>2.043499708175659</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>2.199514865875244</v>
+        <v>2.10905647277832</v>
       </c>
       <c r="C29" t="n">
-        <v>2.176305294036865</v>
+        <v>2.13149619102478</v>
       </c>
       <c r="D29" t="n">
-        <v>2.230329513549805</v>
+        <v>2.0264892578125</v>
       </c>
       <c r="E29" t="n">
-        <v>2.092554092407227</v>
+        <v>2.264668464660645</v>
       </c>
       <c r="F29" t="n">
-        <v>2.226234436035156</v>
+        <v>2.37208890914917</v>
       </c>
       <c r="G29" t="n">
-        <v>2.211363315582275</v>
+        <v>2.172640800476074</v>
       </c>
       <c r="H29" t="n">
-        <v>2.192692756652832</v>
+        <v>2.673639535903931</v>
       </c>
       <c r="I29" t="n">
-        <v>2.265589952468872</v>
+        <v>2.53394079208374</v>
       </c>
       <c r="J29" t="n">
-        <v>2.313748836517334</v>
+        <v>2.396591663360596</v>
       </c>
       <c r="K29" t="n">
-        <v>2.310899496078491</v>
+        <v>2.786218166351318</v>
       </c>
       <c r="L29" t="n">
-        <v>2.22192325592041</v>
+        <v>2.346683025360107</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>2.42798113822937</v>
+        <v>2.265933990478516</v>
       </c>
       <c r="C30" t="n">
-        <v>2.207284927368164</v>
+        <v>2.424523591995239</v>
       </c>
       <c r="D30" t="n">
-        <v>2.133646726608276</v>
+        <v>2.623557090759277</v>
       </c>
       <c r="E30" t="n">
-        <v>2.340933322906494</v>
+        <v>2.528921365737915</v>
       </c>
       <c r="F30" t="n">
-        <v>2.282953023910522</v>
+        <v>2.342167139053345</v>
       </c>
       <c r="G30" t="n">
-        <v>2.242678165435791</v>
+        <v>2.391417026519775</v>
       </c>
       <c r="H30" t="n">
-        <v>2.189196586608887</v>
+        <v>2.433007478713989</v>
       </c>
       <c r="I30" t="n">
-        <v>2.513855457305908</v>
+        <v>2.679009199142456</v>
       </c>
       <c r="J30" t="n">
-        <v>2.383231401443481</v>
+        <v>2.374720811843872</v>
       </c>
       <c r="K30" t="n">
-        <v>2.410650253295898</v>
+        <v>2.398115873336792</v>
       </c>
       <c r="L30" t="n">
-        <v>2.313241100311279</v>
+        <v>2.446137356758117</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1.863295316696167</v>
+        <v>2.004698991775513</v>
       </c>
       <c r="C31" t="n">
-        <v>2.000634431838989</v>
+        <v>2.234795093536377</v>
       </c>
       <c r="D31" t="n">
-        <v>1.951871395111084</v>
+        <v>1.989091157913208</v>
       </c>
       <c r="E31" t="n">
-        <v>1.992684841156006</v>
+        <v>2.022882699966431</v>
       </c>
       <c r="F31" t="n">
-        <v>1.929226160049438</v>
+        <v>1.963212966918945</v>
       </c>
       <c r="G31" t="n">
-        <v>1.892015933990479</v>
+        <v>2.293087482452393</v>
       </c>
       <c r="H31" t="n">
-        <v>2.101071357727051</v>
+        <v>3.455094337463379</v>
       </c>
       <c r="I31" t="n">
-        <v>1.977508544921875</v>
+        <v>2.424850463867188</v>
       </c>
       <c r="J31" t="n">
-        <v>2.467499494552612</v>
+        <v>2.127092123031616</v>
       </c>
       <c r="K31" t="n">
-        <v>2.120005130767822</v>
+        <v>2.058760404586792</v>
       </c>
       <c r="L31" t="n">
-        <v>2.029581260681153</v>
+        <v>2.257356572151184</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>2.212886571884155</v>
+        <v>2.07222056388855</v>
       </c>
       <c r="C32" t="n">
-        <v>2.240694761276245</v>
+        <v>2.288671255111694</v>
       </c>
       <c r="D32" t="n">
-        <v>2.279993772506714</v>
+        <v>2.182915449142456</v>
       </c>
       <c r="E32" t="n">
-        <v>2.084669351577759</v>
+        <v>2.01739764213562</v>
       </c>
       <c r="F32" t="n">
-        <v>2.122385263442993</v>
+        <v>2.165002822875977</v>
       </c>
       <c r="G32" t="n">
-        <v>2.171117067337036</v>
+        <v>2.025829553604126</v>
       </c>
       <c r="H32" t="n">
-        <v>2.320055961608887</v>
+        <v>2.262732982635498</v>
       </c>
       <c r="I32" t="n">
-        <v>2.252811193466187</v>
+        <v>2.047772169113159</v>
       </c>
       <c r="J32" t="n">
-        <v>2.191206932067871</v>
+        <v>2.36998987197876</v>
       </c>
       <c r="K32" t="n">
-        <v>2.101426839828491</v>
+        <v>2.070221185684204</v>
       </c>
       <c r="L32" t="n">
-        <v>2.197724771499634</v>
+        <v>2.150275349617004</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>2.216056346893311</v>
+        <v>2.132059574127197</v>
       </c>
       <c r="C33" t="n">
-        <v>2.117751359939575</v>
+        <v>2.211347579956055</v>
       </c>
       <c r="D33" t="n">
-        <v>2.234279632568359</v>
+        <v>2.111119508743286</v>
       </c>
       <c r="E33" t="n">
-        <v>2.086774110794067</v>
+        <v>2.034807443618774</v>
       </c>
       <c r="F33" t="n">
-        <v>2.19733452796936</v>
+        <v>2.192420959472656</v>
       </c>
       <c r="G33" t="n">
-        <v>2.279470920562744</v>
+        <v>2.192410230636597</v>
       </c>
       <c r="H33" t="n">
-        <v>2.400221824645996</v>
+        <v>2.187423229217529</v>
       </c>
       <c r="I33" t="n">
-        <v>2.305933952331543</v>
+        <v>1.919606447219849</v>
       </c>
       <c r="J33" t="n">
-        <v>2.31972336769104</v>
+        <v>2.265728950500488</v>
       </c>
       <c r="K33" t="n">
-        <v>2.28101658821106</v>
+        <v>2.609385967254639</v>
       </c>
       <c r="L33" t="n">
-        <v>2.243856263160706</v>
+        <v>2.185630989074707</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>1.982303619384766</v>
+        <v>3.157541513442993</v>
       </c>
       <c r="C34" t="n">
-        <v>1.987125635147095</v>
+        <v>5.321145534515381</v>
       </c>
       <c r="D34" t="n">
-        <v>2.039689302444458</v>
+        <v>2.078240871429443</v>
       </c>
       <c r="E34" t="n">
-        <v>1.972853422164917</v>
+        <v>1.944542646408081</v>
       </c>
       <c r="F34" t="n">
-        <v>1.991902589797974</v>
+        <v>2.351076126098633</v>
       </c>
       <c r="G34" t="n">
-        <v>1.918233633041382</v>
+        <v>2.181461811065674</v>
       </c>
       <c r="H34" t="n">
-        <v>2.090041160583496</v>
+        <v>1.970466375350952</v>
       </c>
       <c r="I34" t="n">
-        <v>1.936633825302124</v>
+        <v>2.08721137046814</v>
       </c>
       <c r="J34" t="n">
-        <v>1.919056177139282</v>
+        <v>2.083195447921753</v>
       </c>
       <c r="K34" t="n">
-        <v>2.009492874145508</v>
+        <v>2.112116575241089</v>
       </c>
       <c r="L34" t="n">
-        <v>1.9847332239151</v>
+        <v>2.528699827194214</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>2.576903581619263</v>
+        <v>2.483178853988647</v>
       </c>
       <c r="C35" t="n">
-        <v>2.560058116912842</v>
+        <v>2.755999088287354</v>
       </c>
       <c r="D35" t="n">
-        <v>2.714303016662598</v>
+        <v>2.648257970809937</v>
       </c>
       <c r="E35" t="n">
-        <v>2.571069717407227</v>
+        <v>2.834800004959106</v>
       </c>
       <c r="F35" t="n">
-        <v>2.477609872817993</v>
+        <v>2.733062505722046</v>
       </c>
       <c r="G35" t="n">
-        <v>2.64006495475769</v>
+        <v>3.58948540687561</v>
       </c>
       <c r="H35" t="n">
-        <v>2.522542476654053</v>
+        <v>3.157042980194092</v>
       </c>
       <c r="I35" t="n">
-        <v>2.534015893936157</v>
+        <v>2.783921480178833</v>
       </c>
       <c r="J35" t="n">
-        <v>2.592559337615967</v>
+        <v>2.945014715194702</v>
       </c>
       <c r="K35" t="n">
-        <v>2.441059589385986</v>
+        <v>2.748510122299194</v>
       </c>
       <c r="L35" t="n">
-        <v>2.563018655776978</v>
+        <v>2.867927312850952</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>2.019335746765137</v>
+        <v>2.162987470626831</v>
       </c>
       <c r="C36" t="n">
-        <v>2.187746047973633</v>
+        <v>2.072232484817505</v>
       </c>
       <c r="D36" t="n">
-        <v>3.569787979125977</v>
+        <v>2.046786308288574</v>
       </c>
       <c r="E36" t="n">
-        <v>2.153377294540405</v>
+        <v>2.048292398452759</v>
       </c>
       <c r="F36" t="n">
-        <v>2.104535818099976</v>
+        <v>2.054786205291748</v>
       </c>
       <c r="G36" t="n">
-        <v>1.993974208831787</v>
+        <v>2.186450719833374</v>
       </c>
       <c r="H36" t="n">
-        <v>2.028575897216797</v>
+        <v>2.115124464035034</v>
       </c>
       <c r="I36" t="n">
-        <v>1.935976266860962</v>
+        <v>2.082214832305908</v>
       </c>
       <c r="J36" t="n">
-        <v>2.151646375656128</v>
+        <v>2.085192203521729</v>
       </c>
       <c r="K36" t="n">
-        <v>2.065014362335205</v>
+        <v>2.336591958999634</v>
       </c>
       <c r="L36" t="n">
-        <v>2.2209969997406</v>
+        <v>2.119065904617309</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>2.516023635864258</v>
+        <v>2.539046287536621</v>
       </c>
       <c r="C37" t="n">
-        <v>2.541990041732788</v>
+        <v>2.471221208572388</v>
       </c>
       <c r="D37" t="n">
-        <v>2.447753667831421</v>
+        <v>2.46371603012085</v>
       </c>
       <c r="E37" t="n">
-        <v>2.273850917816162</v>
+        <v>2.687662839889526</v>
       </c>
       <c r="F37" t="n">
-        <v>2.346983671188354</v>
+        <v>2.643265962600708</v>
       </c>
       <c r="G37" t="n">
-        <v>2.489376783370972</v>
+        <v>2.598383903503418</v>
       </c>
       <c r="H37" t="n">
-        <v>2.501929998397827</v>
+        <v>3.43286657333374</v>
       </c>
       <c r="I37" t="n">
-        <v>2.440017938613892</v>
+        <v>2.535040378570557</v>
       </c>
       <c r="J37" t="n">
-        <v>2.415635108947754</v>
+        <v>2.335541486740112</v>
       </c>
       <c r="K37" t="n">
-        <v>2.590494632720947</v>
+        <v>2.216345071792603</v>
       </c>
       <c r="L37" t="n">
-        <v>2.456405639648438</v>
+        <v>2.592308974266052</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>2.658085823059082</v>
+        <v>2.730525970458984</v>
       </c>
       <c r="C38" t="n">
-        <v>2.633858442306519</v>
+        <v>2.839761018753052</v>
       </c>
       <c r="D38" t="n">
-        <v>2.636746168136597</v>
+        <v>2.458243370056152</v>
       </c>
       <c r="E38" t="n">
-        <v>2.644447565078735</v>
+        <v>2.572914123535156</v>
       </c>
       <c r="F38" t="n">
-        <v>2.67473292350769</v>
+        <v>2.757042646408081</v>
       </c>
       <c r="G38" t="n">
-        <v>2.444825172424316</v>
+        <v>3.452796936035156</v>
       </c>
       <c r="H38" t="n">
-        <v>2.611186742782593</v>
+        <v>3.114606857299805</v>
       </c>
       <c r="I38" t="n">
-        <v>2.998181819915771</v>
+        <v>3.084645986557007</v>
       </c>
       <c r="J38" t="n">
-        <v>2.591140031814575</v>
+        <v>2.671693563461304</v>
       </c>
       <c r="K38" t="n">
-        <v>2.555258750915527</v>
+        <v>2.642279386520386</v>
       </c>
       <c r="L38" t="n">
-        <v>2.644846343994141</v>
+        <v>2.832450985908508</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>2.322101593017578</v>
+        <v>2.220860004425049</v>
       </c>
       <c r="C39" t="n">
-        <v>2.341990947723389</v>
+        <v>2.376443386077881</v>
       </c>
       <c r="D39" t="n">
-        <v>2.489293575286865</v>
+        <v>2.657743453979492</v>
       </c>
       <c r="E39" t="n">
-        <v>2.1586012840271</v>
+        <v>2.197405099868774</v>
       </c>
       <c r="F39" t="n">
-        <v>2.492565155029297</v>
+        <v>2.357477426528931</v>
       </c>
       <c r="G39" t="n">
-        <v>2.492486476898193</v>
+        <v>2.334051609039307</v>
       </c>
       <c r="H39" t="n">
-        <v>2.265612125396729</v>
+        <v>2.185915231704712</v>
       </c>
       <c r="I39" t="n">
-        <v>2.391162633895874</v>
+        <v>2.338073492050171</v>
       </c>
       <c r="J39" t="n">
-        <v>2.462306022644043</v>
+        <v>2.163974523544312</v>
       </c>
       <c r="K39" t="n">
-        <v>2.099973678588867</v>
+        <v>2.25076150894165</v>
       </c>
       <c r="L39" t="n">
-        <v>2.351609349250793</v>
+        <v>2.308270573616028</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>2.171559810638428</v>
+        <v>2.234292507171631</v>
       </c>
       <c r="C40" t="n">
-        <v>2.197296142578125</v>
+        <v>2.167488813400269</v>
       </c>
       <c r="D40" t="n">
-        <v>2.241545677185059</v>
+        <v>2.120097160339355</v>
       </c>
       <c r="E40" t="n">
-        <v>2.184471130371094</v>
+        <v>2.059752225875854</v>
       </c>
       <c r="F40" t="n">
-        <v>2.200893640518188</v>
+        <v>2.145535945892334</v>
       </c>
       <c r="G40" t="n">
-        <v>2.199337720870972</v>
+        <v>2.189412593841553</v>
       </c>
       <c r="H40" t="n">
-        <v>2.268239974975586</v>
+        <v>2.26621413230896</v>
       </c>
       <c r="I40" t="n">
-        <v>2.16254997253418</v>
+        <v>2.156518936157227</v>
       </c>
       <c r="J40" t="n">
-        <v>2.178536653518677</v>
+        <v>2.159980535507202</v>
       </c>
       <c r="K40" t="n">
-        <v>2.152784824371338</v>
+        <v>2.212864875793457</v>
       </c>
       <c r="L40" t="n">
-        <v>2.195721554756164</v>
+        <v>2.171215772628784</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>2.60306453704834</v>
+        <v>2.333566904067993</v>
       </c>
       <c r="C41" t="n">
-        <v>2.478181123733521</v>
+        <v>2.547015905380249</v>
       </c>
       <c r="D41" t="n">
-        <v>2.677176237106323</v>
+        <v>2.615329027175903</v>
       </c>
       <c r="E41" t="n">
-        <v>2.508199453353882</v>
+        <v>2.528061866760254</v>
       </c>
       <c r="F41" t="n">
-        <v>2.602771043777466</v>
+        <v>2.51209831237793</v>
       </c>
       <c r="G41" t="n">
-        <v>2.427378177642822</v>
+        <v>2.565962076187134</v>
       </c>
       <c r="H41" t="n">
-        <v>2.339385509490967</v>
+        <v>2.622830152511597</v>
       </c>
       <c r="I41" t="n">
-        <v>2.653534173965454</v>
+        <v>2.6986403465271</v>
       </c>
       <c r="J41" t="n">
-        <v>2.465718507766724</v>
+        <v>2.505122661590576</v>
       </c>
       <c r="K41" t="n">
-        <v>2.350378513336182</v>
+        <v>2.32157301902771</v>
       </c>
       <c r="L41" t="n">
-        <v>2.510578727722168</v>
+        <v>2.525020027160644</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>2.243358135223389</v>
+        <v>2.043786764144897</v>
       </c>
       <c r="C42" t="n">
-        <v>2.064113140106201</v>
+        <v>1.979955196380615</v>
       </c>
       <c r="D42" t="n">
-        <v>2.117473125457764</v>
+        <v>2.015850067138672</v>
       </c>
       <c r="E42" t="n">
-        <v>2.099388837814331</v>
+        <v>2.05825662612915</v>
       </c>
       <c r="F42" t="n">
-        <v>2.065635681152344</v>
+        <v>2.033803939819336</v>
       </c>
       <c r="G42" t="n">
-        <v>2.072482824325562</v>
+        <v>2.036806583404541</v>
       </c>
       <c r="H42" t="n">
-        <v>2.147112369537354</v>
+        <v>1.954007625579834</v>
       </c>
       <c r="I42" t="n">
-        <v>2.310602903366089</v>
+        <v>2.014853239059448</v>
       </c>
       <c r="J42" t="n">
-        <v>2.38151216506958</v>
+        <v>2.085185766220093</v>
       </c>
       <c r="K42" t="n">
-        <v>2.089843273162842</v>
+        <v>2.023834705352783</v>
       </c>
       <c r="L42" t="n">
-        <v>2.159152245521545</v>
+        <v>2.024634051322937</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>2.228122711181641</v>
+        <v>2.325589895248413</v>
       </c>
       <c r="C43" t="n">
-        <v>2.433262348175049</v>
+        <v>2.491148233413696</v>
       </c>
       <c r="D43" t="n">
-        <v>2.460765600204468</v>
+        <v>2.270730495452881</v>
       </c>
       <c r="E43" t="n">
-        <v>2.464879035949707</v>
+        <v>2.347518920898438</v>
       </c>
       <c r="F43" t="n">
-        <v>2.3998122215271</v>
+        <v>2.45026683807373</v>
       </c>
       <c r="G43" t="n">
-        <v>2.431519746780396</v>
+        <v>2.117093801498413</v>
       </c>
       <c r="H43" t="n">
-        <v>2.436788558959961</v>
+        <v>2.457752704620361</v>
       </c>
       <c r="I43" t="n">
-        <v>2.409846305847168</v>
+        <v>2.437299013137817</v>
       </c>
       <c r="J43" t="n">
-        <v>2.511906147003174</v>
+        <v>2.201400518417358</v>
       </c>
       <c r="K43" t="n">
-        <v>2.376792907714844</v>
+        <v>2.156001567840576</v>
       </c>
       <c r="L43" t="n">
-        <v>2.41536955833435</v>
+        <v>2.325480198860169</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>2.282501697540283</v>
+        <v>2.199385166168213</v>
       </c>
       <c r="C44" t="n">
-        <v>2.339346170425415</v>
+        <v>2.235295295715332</v>
       </c>
       <c r="D44" t="n">
-        <v>2.170146942138672</v>
+        <v>2.345017433166504</v>
       </c>
       <c r="E44" t="n">
-        <v>2.149987459182739</v>
+        <v>2.174460411071777</v>
       </c>
       <c r="F44" t="n">
-        <v>2.211446523666382</v>
+        <v>2.400398254394531</v>
       </c>
       <c r="G44" t="n">
-        <v>2.223048210144043</v>
+        <v>2.203373670578003</v>
       </c>
       <c r="H44" t="n">
-        <v>2.323426723480225</v>
+        <v>2.267726182937622</v>
       </c>
       <c r="I44" t="n">
-        <v>2.343498229980469</v>
+        <v>2.213347911834717</v>
       </c>
       <c r="J44" t="n">
-        <v>2.252693891525269</v>
+        <v>2.191439390182495</v>
       </c>
       <c r="K44" t="n">
-        <v>2.179256439208984</v>
+        <v>2.378927707672119</v>
       </c>
       <c r="L44" t="n">
-        <v>2.247535228729248</v>
+        <v>2.260937142372131</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>2.306756258010864</v>
+        <v>2.121086597442627</v>
       </c>
       <c r="C45" t="n">
-        <v>2.099378347396851</v>
+        <v>1.9649817943573</v>
       </c>
       <c r="D45" t="n">
-        <v>2.094962596893311</v>
+        <v>2.021842002868652</v>
       </c>
       <c r="E45" t="n">
-        <v>2.041089296340942</v>
+        <v>1.963480949401855</v>
       </c>
       <c r="F45" t="n">
-        <v>1.979056835174561</v>
+        <v>1.90465259552002</v>
       </c>
       <c r="G45" t="n">
-        <v>1.987659692764282</v>
+        <v>2.102631092071533</v>
       </c>
       <c r="H45" t="n">
-        <v>2.088024616241455</v>
+        <v>2.093175411224365</v>
       </c>
       <c r="I45" t="n">
-        <v>2.047638893127441</v>
+        <v>2.046322345733643</v>
       </c>
       <c r="J45" t="n">
-        <v>1.996026039123535</v>
+        <v>1.996911764144897</v>
       </c>
       <c r="K45" t="n">
-        <v>1.921152591705322</v>
+        <v>2.034826993942261</v>
       </c>
       <c r="L45" t="n">
-        <v>2.056174516677856</v>
+        <v>2.024991154670715</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>2.023108005523682</v>
+        <v>2.008872509002686</v>
       </c>
       <c r="C46" t="n">
-        <v>1.922405481338501</v>
+        <v>1.930574893951416</v>
       </c>
       <c r="D46" t="n">
-        <v>1.961725234985352</v>
+        <v>1.975957870483398</v>
       </c>
       <c r="E46" t="n">
-        <v>1.832535743713379</v>
+        <v>1.839301586151123</v>
       </c>
       <c r="F46" t="n">
-        <v>1.955769777297974</v>
+        <v>1.948028087615967</v>
       </c>
       <c r="G46" t="n">
-        <v>2.10611891746521</v>
+        <v>2.041790008544922</v>
       </c>
       <c r="H46" t="n">
-        <v>2.181783676147461</v>
+        <v>1.98992919921875</v>
       </c>
       <c r="I46" t="n">
-        <v>2.011763334274292</v>
+        <v>1.854769706726074</v>
       </c>
       <c r="J46" t="n">
-        <v>1.910991191864014</v>
+        <v>1.872236967086792</v>
       </c>
       <c r="K46" t="n">
-        <v>1.866154193878174</v>
+        <v>2.070225238800049</v>
       </c>
       <c r="L46" t="n">
-        <v>1.977235555648804</v>
+        <v>1.953168606758118</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>2.540831565856934</v>
+        <v>2.855214357376099</v>
       </c>
       <c r="C47" t="n">
-        <v>2.779852390289307</v>
+        <v>2.840755224227905</v>
       </c>
       <c r="D47" t="n">
-        <v>2.604830026626587</v>
+        <v>2.622357130050659</v>
       </c>
       <c r="E47" t="n">
-        <v>2.398864030838013</v>
+        <v>2.556482076644897</v>
       </c>
       <c r="F47" t="n">
-        <v>3.232467651367188</v>
+        <v>3.029276609420776</v>
       </c>
       <c r="G47" t="n">
-        <v>2.948282718658447</v>
+        <v>3.179899215698242</v>
       </c>
       <c r="H47" t="n">
-        <v>2.622780323028564</v>
+        <v>2.712602615356445</v>
       </c>
       <c r="I47" t="n">
-        <v>3.044764757156372</v>
+        <v>2.528037548065186</v>
       </c>
       <c r="J47" t="n">
-        <v>2.799425601959229</v>
+        <v>2.534031867980957</v>
       </c>
       <c r="K47" t="n">
-        <v>2.700730085372925</v>
+        <v>2.892148017883301</v>
       </c>
       <c r="L47" t="n">
-        <v>2.767282915115357</v>
+        <v>2.775080466270447</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>2.252270221710205</v>
+        <v>2.472215175628662</v>
       </c>
       <c r="C48" t="n">
-        <v>2.349458694458008</v>
+        <v>2.304644107818604</v>
       </c>
       <c r="D48" t="n">
-        <v>2.260887145996094</v>
+        <v>2.309614419937134</v>
       </c>
       <c r="E48" t="n">
-        <v>2.247342348098755</v>
+        <v>2.268723249435425</v>
       </c>
       <c r="F48" t="n">
-        <v>2.356675386428833</v>
+        <v>2.258239269256592</v>
       </c>
       <c r="G48" t="n">
-        <v>2.231813430786133</v>
+        <v>2.330060005187988</v>
       </c>
       <c r="H48" t="n">
-        <v>2.305441617965698</v>
+        <v>2.314604520797729</v>
       </c>
       <c r="I48" t="n">
-        <v>2.358472347259521</v>
+        <v>2.280174732208252</v>
       </c>
       <c r="J48" t="n">
-        <v>2.328752040863037</v>
+        <v>2.25973916053772</v>
       </c>
       <c r="K48" t="n">
-        <v>2.24946117401123</v>
+        <v>2.343509674072266</v>
       </c>
       <c r="L48" t="n">
-        <v>2.294057440757752</v>
+        <v>2.314152431488037</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>2.753186941146851</v>
+        <v>2.370457410812378</v>
       </c>
       <c r="C49" t="n">
-        <v>2.392838954925537</v>
+        <v>2.42381763458252</v>
       </c>
       <c r="D49" t="n">
-        <v>2.451988458633423</v>
+        <v>2.422329187393188</v>
       </c>
       <c r="E49" t="n">
-        <v>2.359716415405273</v>
+        <v>2.494142055511475</v>
       </c>
       <c r="F49" t="n">
-        <v>2.611850500106812</v>
+        <v>2.371472835540771</v>
       </c>
       <c r="G49" t="n">
-        <v>2.375514030456543</v>
+        <v>2.430792570114136</v>
       </c>
       <c r="H49" t="n">
-        <v>2.396360158920288</v>
+        <v>2.54953145980835</v>
       </c>
       <c r="I49" t="n">
-        <v>2.386368989944458</v>
+        <v>2.347511291503906</v>
       </c>
       <c r="J49" t="n">
-        <v>2.607578754425049</v>
+        <v>2.425338983535767</v>
       </c>
       <c r="K49" t="n">
-        <v>2.436185836791992</v>
+        <v>2.368451833724976</v>
       </c>
       <c r="L49" t="n">
-        <v>2.477158904075623</v>
+        <v>2.420384526252747</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>2.118397235870361</v>
+        <v>2.222865581512451</v>
       </c>
       <c r="C50" t="n">
-        <v>2.264998197555542</v>
+        <v>2.032809019088745</v>
       </c>
       <c r="D50" t="n">
-        <v>2.372286796569824</v>
+        <v>2.151011228561401</v>
       </c>
       <c r="E50" t="n">
-        <v>2.341159343719482</v>
+        <v>2.042299747467041</v>
       </c>
       <c r="F50" t="n">
-        <v>2.266597509384155</v>
+        <v>2.291653633117676</v>
       </c>
       <c r="G50" t="n">
-        <v>2.383644819259644</v>
+        <v>2.083678722381592</v>
       </c>
       <c r="H50" t="n">
-        <v>2.184044122695923</v>
+        <v>2.241783618927002</v>
       </c>
       <c r="I50" t="n">
-        <v>2.378677845001221</v>
+        <v>1.925594806671143</v>
       </c>
       <c r="J50" t="n">
-        <v>2.085186958312988</v>
+        <v>2.213350772857666</v>
       </c>
       <c r="K50" t="n">
-        <v>2.365218877792358</v>
+        <v>2.506144523620605</v>
       </c>
       <c r="L50" t="n">
-        <v>2.27602117061615</v>
+        <v>2.171119165420532</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>2.090154886245728</v>
+        <v>2.084186792373657</v>
       </c>
       <c r="C51" t="n">
-        <v>1.950048923492432</v>
+        <v>2.181447267532349</v>
       </c>
       <c r="D51" t="n">
-        <v>2.178715705871582</v>
+        <v>2.054759502410889</v>
       </c>
       <c r="E51" t="n">
-        <v>2.222619295120239</v>
+        <v>2.085180044174194</v>
       </c>
       <c r="F51" t="n">
-        <v>2.130625247955322</v>
+        <v>2.102144479751587</v>
       </c>
       <c r="G51" t="n">
-        <v>2.030028581619263</v>
+        <v>2.025839567184448</v>
       </c>
       <c r="H51" t="n">
-        <v>2.230305671691895</v>
+        <v>2.081184864044189</v>
       </c>
       <c r="I51" t="n">
-        <v>2.219157934188843</v>
+        <v>2.031335830688477</v>
       </c>
       <c r="J51" t="n">
-        <v>2.18026065826416</v>
+        <v>2.139040946960449</v>
       </c>
       <c r="K51" t="n">
-        <v>2.042404413223267</v>
+        <v>2.001899719238281</v>
       </c>
       <c r="L51" t="n">
-        <v>2.127432131767273</v>
+        <v>2.078701901435852</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.331927032470703</v>
+        <v>2.300528512001037</v>
       </c>
       <c r="C52" t="n">
-        <v>2.306360998153687</v>
+        <v>2.361169075965881</v>
       </c>
       <c r="D52" t="n">
-        <v>2.381556129455566</v>
+        <v>2.269445171356201</v>
       </c>
       <c r="E52" t="n">
-        <v>2.280641703605652</v>
+        <v>2.262219362258911</v>
       </c>
       <c r="F52" t="n">
-        <v>2.350072703361511</v>
+        <v>2.291458883285522</v>
       </c>
       <c r="G52" t="n">
-        <v>2.309349722862243</v>
+        <v>2.335869312286377</v>
       </c>
       <c r="H52" t="n">
-        <v>2.325509943962097</v>
+        <v>2.40446943283081</v>
       </c>
       <c r="I52" t="n">
-        <v>2.3567254114151</v>
+        <v>2.294362058639527</v>
       </c>
       <c r="J52" t="n">
-        <v>2.364160251617432</v>
+        <v>2.286675410270691</v>
       </c>
       <c r="K52" t="n">
-        <v>2.321372518539428</v>
+        <v>2.308954267501831</v>
       </c>
       <c r="L52" t="n">
-        <v>2.332767641544342</v>
+        <v>2.311515148639679</v>
       </c>
     </row>
   </sheetData>
